--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Left Out" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Check By Hand'!$A$1:$G$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Check By Hand'!$A$1:$G$204</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Manual Watch'!$A$1:$G$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Priority'!$A$1:$J$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$167</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G203"/>
+  <dimension ref="A1:G204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Stanford Pre-Collegiate Studies jobs (SUMaC RC / TA)</t>
+          <t>Stanford Digital Economy Lab student research assistant positions</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
@@ -6826,22 +6826,22 @@
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>Periodic; none open on 2026-10-08</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>'approximately 30 degree-seeking credits'</t>
+          <t>Stanford undergrads and grads</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>https://spcs.stanford.edu/jobs</t>
+          <t>https://digitaleconomy.stanford.edu/about/careers-and-opportunities/</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: RC posting needs 'completion of approximately 30 degree-seeking credits ... majoring in mathematics or ... advanced coursework' - probably met by spring of first year, confirm by hand. The Instructional Assistant posting returned 403.</t>
+          <t>Verified 2026-10-08: 'we offer a small number of opportunities for undergraduate and graduate students, primarily for current Stanford students ... Research assistant positions open periodically throughout the year'. On 2026-10-08: 'There are currently no open opportunities at the Lab, but this page will be updated when they become available.'</t>
         </is>
       </c>
     </row>
@@ -6853,118 +6853,118 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Bloomberg First Year Insights</t>
+          <t>Stanford Pre-Collegiate Studies jobs (SUMaC RC / TA)</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>First-years (unverified)</t>
+          <t>'approximately 30 degree-seeking credits'</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/company/careers/</t>
+          <t>https://spcs.stanford.edu/jobs</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>Found 2026-09-26 on university early-insight lists. Every bloomberg.com/company path returns 403 to this client; bloomberg.avature.net is the experienced-hire board with no student postings.</t>
+          <t>Verified 2026-09-26: RC posting needs 'completion of approximately 30 degree-seeking credits ... majoring in mathematics or ... advanced coursework' - probably met by spring of first year, confirm by hand. The Instructional Assistant posting returned 403.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>Bloomberg First Year Insights</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>First-years (unverified)</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/company/careers/</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr">
+        <is>
+          <t>Found 2026-09-26 on university early-insight lists. Every bloomberg.com/company path returns 403 to this client; bloomberg.avature.net is the experienced-hire board with no student postings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
           <t>VIA CLUB</t>
         </is>
       </c>
-      <c r="B175" s="3" t="inlineStr">
+      <c r="B176" s="3" t="inlineStr">
         <is>
           <t>Rotman International Trading Competition</t>
         </is>
       </c>
-      <c r="C175" s="3" t="inlineStr">
+      <c r="C176" s="3" t="inlineStr">
         <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="D175" s="3" t="inlineStr">
+      <c r="D176" s="3" t="inlineStr">
         <is>
           <t>Fall, via your university</t>
         </is>
       </c>
-      <c r="E175" s="3" t="inlineStr">
+      <c r="E176" s="3" t="inlineStr">
         <is>
           <t>University-sponsored team</t>
         </is>
       </c>
-      <c r="F175" s="4" t="inlineStr">
+      <c r="F176" s="4" t="inlineStr">
         <is>
           <t>https://www.rotman.utoronto.ca/</t>
         </is>
       </c>
-      <c r="G175" s="3" t="inlineStr">
+      <c r="G176" s="3" t="inlineStr">
         <is>
           <t>40+ universities, RIT Market Simulator. Entry runs through Traders @ Stanford, not by individual application.</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="6" t="inlineStr">
-        <is>
-          <t>APPLIED - too early</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>NISA Investment Advisors - Intern</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="inlineStr">
-        <is>
-          <t>Local (St. Louis)</t>
-        </is>
-      </c>
-      <c r="D176" s="3" t="inlineStr">
-        <is>
-          <t>Fall-winter</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="inlineStr">
-        <is>
-          <t>Prefers Winter 2026 / Spring 2027 grads</t>
-        </is>
-      </c>
-      <c r="F176" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.nisa.com/early-careers</t>
-        </is>
-      </c>
-      <c r="G176" s="3" t="inlineStr">
-        <is>
-          <t>Clayton MO, 10 min from home. Real quant work: Monte Carlo, regression, proprietary modelling. Reapply each cycle.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>APPLIED - too early</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>Edward Jones Internship</t>
+          <t>NISA Investment Advisors - Intern</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
@@ -6974,22 +6974,22 @@
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Fall-winter</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Juniors</t>
+          <t>Prefers Winter 2026 / Spring 2027 grads</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>https://careers.edwardjones.com/career-areas/students-and-recent-grads/</t>
+          <t>https://careers.nisa.com/early-careers</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>10-week program, St. Louis or Tempe.</t>
+          <t>Clayton MO, 10 min from home. Real quant work: Monte Carlo, regression, proprietary modelling. Reapply each cycle.</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Stifel - Institutional Group Internship</t>
+          <t>Edward Jones Internship</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>~Nov, rolling per office/desk</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>https://www.stifel.com/careers/internships</t>
+          <t>https://careers.edwardjones.com/career-areas/students-and-recent-grads/</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>9-10 weeks, St. Louis HQ. Prior cycle opened Nov 16.</t>
+          <t>10-week program, St. Louis or Tempe.</t>
         </is>
       </c>
     </row>
@@ -7038,32 +7038,32 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Research (DESRES) STEM Fellowship</t>
+          <t>Stifel - Institutional Group Internship</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Local (St. Louis)</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>Winter-spring</t>
+          <t>~Nov, rolling per office/desk</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Rising sophomore+</t>
+          <t>Juniors</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>https://www.deshawresearch.com/stemfellowship/</t>
+          <t>https://www.stifel.com/careers/internships</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>Open to RISING sophomores - a first-year qualifies in spring 2027. Computational biochemistry entity, not the fund. | Checked 2026-09-26: now redirects to deshawresearch.com/joining.html, which mentions only summer internships. Kept: it may reopen.</t>
+          <t>9-10 weeks, St. Louis HQ. Prior cycle opened Nov 16.</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>HRT Sophomore Winternship</t>
+          <t>D. E. Shaw Research (DESRES) STEM Fellowship</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -7085,22 +7085,22 @@
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Winter-spring</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Rising sophomore+</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
+          <t>https://www.deshawresearch.com/stemfellowship/</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>January, 2-4 weeks, Python/C++.</t>
+          <t>Open to RISING sophomores - a first-year qualifies in spring 2027. Computational biochemistry entity, not the fund. | Checked 2026-09-26: now redirects to deshawresearch.com/joining.html, which mentions only summer internships. Kept: it may reopen.</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Morgan Stanley Investment Management Sophomore Summer Analyst Program - Private Credit &amp; Equity (New York)</t>
+          <t>HRT Sophomore Winternship</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -7122,22 +7122,22 @@
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>2027 cycle closed Sep 25 2026; expect the 2028 cycle to open around Aug-Sep 2027</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Sophomore - 2027 cycle wanted graduation Dec 2028-Jun 2029</t>
+          <t>2nd year</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?ftq=Sophomore</t>
+          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - a class of 2030 student is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
+          <t>January, 2-4 weeks, Python/C++.</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Capital Markets</t>
+          <t>Morgan Stanley Investment Management Sophomore Summer Analyst Program - Private Credit &amp; Equity (New York)</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -7159,20 +7159,24 @@
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>2027 cycle closed Sep 25 2026; expect the 2028 cycle to open around Aug-Sep 2027</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Sophomore - 2027 cycle wanted graduation Dec 2028-Jun 2029</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="G182" s="3" t="inlineStr"/>
+          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?ftq=Sophomore</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="inlineStr">
+        <is>
+          <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - a class of 2030 student is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
@@ -7182,7 +7186,7 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Growth Equity</t>
+          <t>SIG Sophomore Discovery Day - Capital Markets</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -7215,7 +7219,7 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Technology</t>
+          <t>SIG Sophomore Discovery Day - Growth Equity</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -7248,7 +7252,7 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Technology Infrastructure</t>
+          <t>SIG Sophomore Discovery Day - Technology</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -7281,7 +7285,7 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Trading</t>
+          <t>SIG Sophomore Discovery Day - Technology Infrastructure</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -7304,11 +7308,7 @@
           <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
-      <c r="G186" s="3" t="inlineStr">
-        <is>
-          <t>Reports say includes an interview, unlike the freshman event.</t>
-        </is>
-      </c>
+      <c r="G186" s="3" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Undergraduate Scholarship</t>
+          <t>SIG Sophomore Discovery Day - Trading</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -7333,17 +7333,17 @@
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>3rd year of 4-year degree</t>
+          <t>2nd year</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>Merit-based (resume, transcript, letters). Guarantees a first-round internship interview.</t>
+          <t>Reports say includes an interview, unlike the freshman event.</t>
         </is>
       </c>
     </row>
@@ -7355,32 +7355,32 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Berkeley SUPERB-AI4E REU</t>
+          <t>Two Sigma Undergraduate Scholarship</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Rising juniors and seniors; US citizens or permanent residents</t>
+          <t>3rd year of 4-year degree</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>https://eecs.berkeley.edu/resources/undergrads/undergraduate-research/superb/</t>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>NSF REU site in EECS at UC Berkeley. Page states: US citizens or permanent residents who are rising juniors or seniors with some upper-division EECS coursework, so a first-year is not yet eligible.</t>
+          <t>Merit-based (resume, transcript, letters). Guarantees a first-round internship interview.</t>
         </is>
       </c>
     </row>
@@ -7392,32 +7392,32 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>Stanford VPUE Major Grant</t>
+          <t>Berkeley SUPERB-AI4E REU</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Faculty mentor letter due Mar 8, 2027</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Priority to juniors</t>
+          <t>Rising juniors and seniors; US citizens or permanent residents</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>https://undergradresearch.stanford.edu/</t>
+          <t>https://eecs.berkeley.edu/resources/undergrads/undergraduate-research/superb/</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>$8,500 full-time summer. No GPA requirement.</t>
+          <t>NSF REU site in EECS at UC Berkeley. Page states: US citizens or permanent residents who are rising juniors or seniors with some upper-division EECS coursework, so a first-year is not yet eligible.</t>
         </is>
       </c>
     </row>
@@ -7429,49 +7429,49 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Wells Fargo Sophomore Experience</t>
+          <t>Stanford VPUE Major Grant</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Faculty mentor letter due Mar 8, 2027</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Sophomores</t>
+          <t>Priority to juniors</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>https://talent.wellsfargojobs.com/flows/sdfp2026</t>
+          <t>https://undergradresearch.stanford.edu/</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>Found 2026-09-26; formerly the Sophomore Discovery Fellowship. The flow URL returns 403 to this client and the undergraduate programmes page carries no programme text.</t>
+          <t>$8,500 full-time summer. No GPA requirement.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>LOW VALUE</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>Limex Challenge</t>
+          <t>Wells Fargo Sophomore Experience</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
@@ -7481,17 +7481,17 @@
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Sophomores</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>https://challenges.limex.com/</t>
+          <t>https://talent.wellsfargojobs.com/flows/sdfp2026</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>Retail-facing algorithmic trading challenge platform. Not probed; low expected signal. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Found 2026-09-26; formerly the Sophomore Discovery Fellowship. The flow URL returns 403 to this client and the undergraduate programmes page carries no programme text.</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Quant Tekel QT Funded Elite Trader Competition</t>
+          <t>Limex Challenge</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>https://qtfunded.quanttekel.com/online-trading-championship</t>
+          <t>https://challenges.limex.com/</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>A funded-trader / prop-firm style online championship. These are generally marketing funnels for paid evaluations rather than recruiting credentials - weak signal relative to the time. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Retail-facing algorithmic trading challenge platform. Not probed; low expected signal. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Quantegies Global Quant Competition</t>
+          <t>Quant Tekel QT Funded Elite Trader Competition</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>https://quantegies.com/</t>
+          <t>https://qtfunded.quanttekel.com/online-trading-championship</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>Little published detail and not probed during ingest; unclear whether it is a recruiting-relevant competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>A funded-trader / prop-firm style online championship. These are generally marketing funnels for paid evaluations rather than recruiting credentials - weak signal relative to the time. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Battle of the Quants (NYC spring / London fall 2026)</t>
+          <t>Quantegies Global Quant Competition</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
@@ -7597,12 +7597,12 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>https://battleofthequants.com/new-york-city-2026</t>
+          <t>https://quantegies.com/</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>Industry conference for allocators and fund managers rather than a student event; typically paid admission. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Little published detail and not probed during ingest; unclear whether it is a recruiting-relevant competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>CMF Select New York 2026</t>
+          <t>Battle of the Quants (NYC spring / London fall 2026)</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>https://global-cmf.com/cmfselectnewyork2026</t>
+          <t>https://battleofthequants.com/new-york-city-2026</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Industry conference for allocators and fund managers rather than a student event; typically paid admission. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Future Investment Manager Academy (FIMA)</t>
+          <t>CMF Select New York 2026</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>https://fima.partners/</t>
+          <t>https://global-cmf.com/cmfselectnewyork2026</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>Not probed during ingest; unclear format and eligibility. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>FutureAlpha / QuantStrats 2026</t>
+          <t>Future Investment Manager Academy (FIMA)</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>https://www.alphaevents.com/events-futurealphaglobal</t>
+          <t>https://fima.partners/</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Not probed during ingest; unclear format and eligibility. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>QWAFAFEW / QWAFAxNEW chapters</t>
+          <t>FutureAlpha / QuantStrats 2026</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -7745,12 +7745,12 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>https://www.qwafafew.org/</t>
+          <t>https://www.alphaevents.com/events-futurealphaglobal</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>Professional quant networking chapters. Open but aimed at practitioners; low signal for a first-year, though a local chapter could be worth one visit. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Tapia Conference</t>
+          <t>QWAFAFEW / QWAFAxNEW chapters</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
@@ -7772,22 +7772,22 @@
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Open, but serves underrepresented groups in computing</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>https://tapiaconference.cmd-it.org/</t>
+          <t>https://www.qwafafew.org/</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>Open to attend; low relative value for a first-year.</t>
+          <t>Professional quant networking chapters. Open but aimed at practitioners; low signal for a first-year, though a local chapter could be worth one visit. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7799,69 +7799,69 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
+          <t>Tapia Conference</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>Spring</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>Open, but serves underrepresented groups in computing</t>
+        </is>
+      </c>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t>https://tapiaconference.cmd-it.org/</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>Open to attend; low relative value for a first-year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
           <t>PwC AI Externship (via Extern)</t>
         </is>
       </c>
-      <c r="C200" s="3" t="inlineStr">
+      <c r="C201" s="3" t="inlineStr">
         <is>
           <t>Tech internship</t>
         </is>
       </c>
-      <c r="D200" s="3" t="inlineStr">
+      <c r="D201" s="3" t="inlineStr">
         <is>
           <t>Rolling</t>
         </is>
       </c>
-      <c r="E200" s="3" t="inlineStr">
+      <c r="E201" s="3" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="F200" s="4" t="inlineStr">
+      <c r="F201" s="4" t="inlineStr">
         <is>
           <t>https://www.extern.com/pwc-ai-externships</t>
         </is>
       </c>
-      <c r="G200" s="3" t="inlineStr">
+      <c r="G201" s="3" t="inlineStr">
         <is>
           <t>4 weeks, ~5 hrs/wk, $100 stipend. Aimed at career changers with empty resumes. The in-person PwC AI Workshop ($50) is a cheaper afternoon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
-        </is>
-      </c>
-      <c r="B201" s="3" t="inlineStr">
-        <is>
-          <t>Duke Career Hub early-insight table</t>
-        </is>
-      </c>
-      <c r="C201" s="3" t="inlineStr">
-        <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D201" s="3" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="E201" s="3" t="inlineStr">
-        <is>
-          <t>First-year/sophomore</t>
-        </is>
-      </c>
-      <c r="F201" s="4" t="inlineStr">
-        <is>
-          <t>https://careerhub.students.duke.edu/</t>
-        </is>
-      </c>
-      <c r="G201" s="3" t="inlineStr">
-        <is>
-          <t>Public list of early insight programs by target year.</t>
         </is>
       </c>
     </row>
@@ -7873,7 +7873,7 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Yale 'Gorick's List' for quant trading</t>
+          <t>Duke Career Hub early-insight table</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -7888,55 +7888,92 @@
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>First-year/sophomore</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>https://ocs.yale.edu/resources/goricks-list-4/</t>
-        </is>
-      </c>
-      <c r="G202" s="3" t="inlineStr"/>
+          <t>https://careerhub.students.duke.edu/</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="inlineStr">
+        <is>
+          <t>Public list of early insight programs by target year.</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>Yale 'Gorick's List' for quant trading</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F203" s="4" t="inlineStr">
+        <is>
+          <t>https://ocs.yale.edu/resources/goricks-list-4/</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
           <t>USE WEEKLY</t>
         </is>
       </c>
-      <c r="B203" s="3" t="inlineStr">
+      <c r="B204" s="3" t="inlineStr">
         <is>
           <t>OpenQuant job board + newsletter</t>
         </is>
       </c>
-      <c r="C203" s="3" t="inlineStr">
+      <c r="C204" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D203" s="3" t="inlineStr">
+      <c r="D204" s="3" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="E203" s="3" t="inlineStr">
+      <c r="E204" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F203" s="4" t="inlineStr">
+      <c r="F204" s="4" t="inlineStr">
         <is>
           <t>https://openquant.co/</t>
         </is>
       </c>
-      <c r="G203" s="3" t="inlineStr">
+      <c r="G204" s="3" t="inlineStr">
         <is>
           <t>Best-maintained source found. See openquant.co/blog/quantitative-finance-events-2026 for the events roundup.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G203"/>
+  <autoFilter ref="A1:G204"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -8137,6 +8174,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId197"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId200"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11942,7 +11980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12084,273 +12122,273 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Already watched by berkeley-trading-competition</t>
+          <t>Already watched by apollo-workday</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Berkeley Trading Competition</t>
+          <t>Apollo careers board</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Finance program</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>https://traders.studentorg.berkeley.edu/competition.html</t>
+          <t>https://athene.wd5.myworkdayjobs.com/apollononpubliccareersite</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>West Coast's premier event, $20,000 pool, 45 min from campus. Best convenience-to-value ratio on this list. | Checked 2026-09-26: the listed competition.html URL returns 404; the live page is traders.studentorg.berkeley.edu/competition/, which is what is watched. The listed URL is kept.</t>
+          <t>Apollo's Workday board (hosted on the Athene tenant); linked from Extern's 2027 sophomore guide. 96 postings on 2026-10-11 including '2027 Sophomore Summer Analyst'.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Already watched by big-pitch-comp</t>
+          <t>Already watched by baincapital-workday</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>The BIG Pitch Comp (Boulevard Investment Group, SMU Cox)</t>
+          <t>Bain Capital careers board</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Finance program</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>https://www.blvdinvestmentgroup.org/thebigpitchcomp</t>
+          <t>https://baincapital.wd1.myworkdayjobs.com/External_Public</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08 on the official pages, still describing the 2026 edition: "A national stock pitch competition for collegiate undergraduates"; "Team size: 2-4 undergraduate students"; the apply page says "Undergraduate-only competition. Cross-school teams allowed." Deck plus 3-minute thesis video on one U.S.-listed equity over $1B. $20,000 prize pool ($10k / $6.5k / $3.5k); finalists must travel to Dallas and BIG pays one hotel night (Apr 10). No class-year restriction stated. The separate "2026 Freshmen Pitch Comp" on the same site is for SMU students only and is not tracked.</t>
+          <t>Bain Capital's Workday board. Per Extern 2026-10-08: Investors of Tomorrow for sophomores, apply by Oct 25 2026; Summer Analyst (Path into Private Equity) went live early January last cycle.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Already watched by bny-pre-internship</t>
+          <t>Already watched by barclays-discovery</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>BNY Freshman Jumpstart</t>
+          <t>Barclays Discovery Programme</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Finance program</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>https://www.bny.com/corporate/global/en/about-us/careers/students/pre-internship.html</t>
+          <t>https://search.jobs.barclays/discovery</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'Undergraduate first-year students ... with an expected graduation date of December 2029 or May 2030.' Two virtual half-days, business &amp; corporate functions track. Low effort, low depth.</t>
+          <t>Barclays's Discovery listings (US and UK). Simplify's list gives about a dozen sophomore Discovery programmes across banking, markets and research; it also names a Freshman Foundation.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Already watched by bofa-campus-events</t>
+          <t>Already watched by berkeley-trading-competition</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Bank of America campus events (Early Insights)</t>
+          <t>Berkeley Trading Competition</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>https://bankcampuscareers.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
+          <t>https://traders.studentorg.berkeley.edu/competition.html</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Oleeo (tal.net) Atom feed of campus events, 18 entries, answers the honest User-Agent. Also available: vacancy/1/feed (152 entries) and a JSON API at careers.bankofamerica.com/services/campusjobssearchservlet.</t>
+          <t>West Coast's premier event, $20,000 pool, 45 min from campus. Best convenience-to-value ratio on this list. | Checked 2026-09-26: the listed competition.html URL returns 404; the live page is traders.studentorg.berkeley.edu/competition/, which is what is watched. The listed URL is kept.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Already watched by bridgewater-students</t>
+          <t>Already watched by big-pitch-comp</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Bridgewater Investment Immersion Program</t>
+          <t>The BIG Pitch Comp (Boulevard Investment Group, SMU Cox)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>https://www.bridgewater.com/working-at-bridgewater/students</t>
+          <t>https://www.blvdinvestmentgroup.org/thebigpitchcomp</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>3 days onsite in Westport. Explicitly 'second year of a 4-year degree'.</t>
+          <t>Verified 2026-10-08 on the official pages, still describing the 2026 edition: "A national stock pitch competition for collegiate undergraduates"; "Team size: 2-4 undergraduate students"; the apply page says "Undergraduate-only competition. Cross-school teams allowed." Deck plus 3-minute thesis video on one U.S.-listed equity over $1B. $20,000 prize pool ($10k / $6.5k / $3.5k); finalists must travel to Dallas and BIG pays one hotel night (Apr 10). No class-year restriction stated. The separate "2026 Freshmen Pitch Comp" on the same site is for SMU students only and is not tracked.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Already watched by builtin-data-analytics</t>
+          <t>Already watched by blackstone-campus-workday</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Built In data and analytics internships</t>
+          <t>Blackstone campus board</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
+          <t>Finance program</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>https://builtin.com/jobs/data-analytics/internship</t>
+          <t>https://blackstone.wd1.myworkdayjobs.com/Blackstone_Campus_Careers</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Front page of Built In's data and analytics internship listings, newest first (about 14-25 cards), watched as a what's-new feed rather than a full list: the site returns HTTP 429 after roughly 70 requests at one a second, so a full crawl is not polite. Measured 2026-10-01 across a deeper crawl: most of its in-field internships were not on Simplify, but many are generic internships at large non-technology employers.</t>
+          <t>Blackstone's campus Workday board, 31 postings on 2026-10-11. Its named sophomore programmes (Diverse Leaders, Future Women Leaders) are identity-targeted; the board also carries general summer analyst roles.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Already watched by builtin-dev-engineering</t>
+          <t>Already watched by bny-pre-internship</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Built In software engineering internships</t>
+          <t>BNY Freshman Jumpstart</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>USE</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>https://builtin.com/jobs/dev-engineering/internship</t>
+          <t>https://www.bny.com/corporate/global/en/about-us/careers/students/pre-internship.html</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Front page of Built In's software engineering internship listings, newest first (about 14-25 cards), watched as a what's-new feed rather than a full list: the site returns HTTP 429 after roughly 70 requests at one a second, so a full crawl is not polite. Measured 2026-10-01 across a deeper crawl: most of its in-field internships were not on Simplify, but many are generic internships at large non-technology employers.</t>
+          <t>Verified 2026-09-30: 'Undergraduate first-year students ... with an expected graduation date of December 2029 or May 2030.' Two virtual half-days, business &amp; corporate functions track. Low effort, low depth.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Already watched by builtin-finance</t>
+          <t>Already watched by bofa-campus-events</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Built In finance internships</t>
+          <t>Bank of America campus events (Early Insights)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>https://builtin.com/jobs/finance/internship</t>
+          <t>https://bankcampuscareers.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Front page of Built In's finance internship listings, newest first (about 14-25 cards), watched as a what's-new feed rather than a full list: the site returns HTTP 429 after roughly 70 requests at one a second, so a full crawl is not polite. Measured 2026-10-01 across a deeper crawl: most of its in-field internships were not on Simplify, but many are generic internships at large non-technology employers.</t>
+          <t>Verified 2026-09-26: Oleeo (tal.net) Atom feed of campus events, 18 entries, answers the honest User-Agent. Also available: vacancy/1/feed (152 entries) and a JSON API at careers.bankofamerica.com/services/campusjobssearchservlet.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Already watched by calhacks</t>
+          <t>Already watched by bofa-student-programs</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Cal Hacks</t>
+          <t>Bank of America student programs</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Finance program</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -12360,56 +12398,56 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>https://www.calhacks.io/</t>
+          <t>https://careers.bankofamerica.com/en-us/students/programs</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'Cal Hacks is open to undergraduate and graduate students as well as new grads of under 1 year from all colleges and universities.' Travel: 'This year, we will be offering travel stipends to a limited number of hackers with regional caps based on the region you are coming from'; most attendees get there themselves (Caltrain, BART). Run by Hackers@Berkeley; held in San Francisco.</t>
+          <t>The programme index; Simplify's list names Ignite With STEM (freshman/sophomore) and the Global Banking &amp; Markets Sophomore Summer Program. Complements the bofa-campus-events tal.net feed.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Already watched by capitalone-early-career</t>
+          <t>Already watched by bridgewater-students</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Capital One Analyst / Tech / Product Summits</t>
+          <t>Bridgewater Investment Immersion Program</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>https://www.capitalonecareers.com/get-ahead-with-early-career-programs-for-students</t>
+          <t>https://www.bridgewater.com/working-at-bridgewater/students</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Analyst Summit 'First-year students or sophomores pursuing a quantitative/STEM major'; Tech Summit 'Sophomores with beginner coding experience'. Separate from the Capital One TEIP row.</t>
+          <t>3 days onsite in Westport. Explicitly 'second year of a 4-year degree'.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cerebralvalley-sf-events</t>
+          <t>Already watched by builtin-data-analytics</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Cerebral Valley SF &amp; Bay Area AI events calendar</t>
+          <t>Built In data and analytics internships</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -12417,95 +12455,95 @@
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>USE</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>https://cerebralvalley.ai/events/san-francisco</t>
+          <t>https://builtin.com/jobs/data-analytics/internship</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: Cerebral Valley's SF and Bay Area AI event feed, mixing hackathons with talks and meetups, e.g. 'The Recursive Agents Hackathon' (Oct 17, Shack15 SF; 'All attendees must apply and be approved') and 'Intelligence at Work Hackathon' (Oct 23, Menlo Park). Not student-specific; check each event's own terms.</t>
+          <t>Front page of Built In's data and analytics internship listings, newest first (about 14-25 cards), watched as a what's-new feed rather than a full list: the site returns HTTP 429 after roughly 70 requests at one a second, so a full crawl is not polite. Measured 2026-10-01 across a deeper crawl: most of its in-field internships were not on Simplify, but many are generic internships at large non-technology employers.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Already watched by citi-pre-internships</t>
+          <t>Already watched by builtin-dev-engineering</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Citi Freshman Discovery</t>
+          <t>Built In software engineering internships</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Tracker / resource</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>USE</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.citi.com/early-career-programs-pre-internships</t>
+          <t>https://builtin.com/jobs/dev-engineering/internship</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'All first-year students in a four-year bachelor's degree program from a US accredited institution, regardless of major.' 3-day virtual introduction to financial services.</t>
+          <t>Front page of Built In's software engineering internship listings, newest first (about 14-25 cards), watched as a what's-new feed rather than a full list: the site returns HTTP 429 after roughly 70 requests at one a second, so a full crawl is not polite. Measured 2026-10-01 across a deeper crawl: most of its in-field internships were not on Simplify, but many are generic internships at large non-technology employers.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cmu-riss</t>
+          <t>Already watched by builtin-finance</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>CMU Robotics Institute Summer Scholars (RISS)</t>
+          <t>Built In finance internships</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>USE</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>https://riss.ri.cmu.edu/</t>
+          <t>https://builtin.com/jobs/finance/internship</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>11-week summer research immersion for undergraduates at CMU's Robotics Institute.</t>
+          <t>Front page of Built In's finance internship listings, newest first (about 14-25 cards), watched as a what's-new feed rather than a full list: the site returns HTTP 429 after roughly 70 requests at one a second, so a full crawl is not polite. Measured 2026-10-01 across a deeper crawl: most of its in-field internships were not on Simplify, but many are generic internships at large non-technology employers.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Already watched by comap-mcm</t>
+          <t>Already watched by calhacks</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>COMAP MCM/ICM</t>
+          <t>Cal Hacks</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -12520,61 +12558,61 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>https://www.contest.comap.com/undergraduate/contests/</t>
+          <t>https://www.calhacks.io/</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'high school students and college undergraduates'; 2027 contest 28 Jan - 1 Feb.</t>
+          <t>Verified 2026-10-08: 'Cal Hacks is open to undergraduate and graduate students as well as new grads of under 1 year from all colleges and universities.' Travel: 'This year, we will be offering travel stipends to a limited number of hackers with regional caps based on the region you are coming from'; most attendees get there themselves (Caltrain, BART). Run by Hackers@Berkeley; held in San Francisco.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cornell-trading-competition</t>
+          <t>Already watched by capitalone-early-career</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Cornell Trading Competition</t>
+          <t>Capital One Analyst / Tech / Product Summits</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>https://cornellquantfund.org/competition</t>
+          <t>https://www.capitalonecareers.com/get-ahead-with-early-career-programs-for-students</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Teams of 4, NO EXPERIENCE NECESSARY, $10k+ prizes, Cornell Tech NYC. Case packets released 2 weeks early.</t>
+          <t>Verified 2026-09-26: Analyst Summit 'First-year students or sophomores pursuing a quantitative/STEM major'; Tech Summit 'Sophomores with beginner coding experience'. Separate from the Capital One TEIP row.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cra-dreu</t>
+          <t>Already watched by cerebralvalley-sf-events</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>CRA DREU</t>
+          <t>Cerebral Valley SF &amp; Bay Area AI events calendar</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Tracker / resource</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -12584,29 +12622,29 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>https://cra.org/cra-wp/dreu/</t>
+          <t>https://cerebralvalley.ai/events/san-francisco</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'High school graduates who have been accepted ... are also eligible'; priority to CS majors. Large page (94K chars).</t>
+          <t>Verified 2026-10-08: Cerebral Valley's SF and Bay Area AI event feed, mixing hackathons with talks and meetups, e.g. 'The Recursive Agents Hackathon' (Oct 17, Shack15 SF; 'All attendees must apply and be approved') and 'Intelligence at Work Hackathon' (Oct 23, Menlo Park). Not student-specific; check each event's own terms.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cs-social-good-fellowships</t>
+          <t>Already watched by citi-pre-internships</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>CS+Social Good Summer Fellowships</t>
+          <t>Citi Freshman Discovery</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -12616,125 +12654,125 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>https://cardinalservice.stanford.edu/opportunities/cssocial-good-summer-fellowships</t>
+          <t>https://jobs.citi.com/early-career-programs-pre-internships</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30 from the 2026 SOLO listing: 'enrolled as a first-year, sophomore, or junior ... must have completed CS 106B by the end of Spring Quarter.' $7,000 base stipend, full-time summer with a tech-for-good partner. Cardinal Quarter.</t>
+          <t>Verified 2026-09-30: 'All first-year students in a four-year bachelor's degree program from a US accredited institution, regardless of major.' 3-day virtual introduction to financial services.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Already watched by curis</t>
+          <t>Already watched by cmu-riss</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Stanford CURIS</t>
+          <t>CMU Robotics Institute Summer Scholars (RISS)</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>https://curis.stanford.edu/</t>
+          <t>https://riss.ri.cmu.edu/</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>CS dept paid summer research. Project list posted late Jan. Also lists year-round projects for units or hourly pay. | Checked 2026-09-26: now watched with render_js - the page is client-rendered and yields 1,264 chars in the browser.</t>
+          <t>11-week summer research immersion for undergraduates at CMU's Robotics Institute.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Already watched by datasurf</t>
+          <t>Already watched by comap-mcm</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Stanford DataSURF (formerly SURP-Stats)</t>
+          <t>COMAP MCM/ICM</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>https://datasciencemajor.stanford.edu/research-impact/data-science-undergraduate-research-focus</t>
+          <t>https://www.contest.comap.com/undergraduate/contests/</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'Stanford undergraduate students from any department who meet the prerequisites are encouraged to apply' (examples: STATS 60, MATH 51-53, CS 106A/B). 10 weeks, $8,500 stipend plus need-based supplement.</t>
+          <t>Verified 2026-09-26: 'high school students and college undergraduates'; 2027 contest 28 Jan - 1 Feb.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Already watched by deshaw-campus</t>
+          <t>Already watched by cornell-trading-competition</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Nexus Fellowship</t>
+          <t>Cornell Trading Competition</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://cornellquantfund.org/competition</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>THE one for a first-year to target the following year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging. | Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>Teams of 4, NO EXPERIENCE NECESSARY, $10k+ prizes, Cornell Tech NYC. Case packets released 2 weeks early.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Already watched by deshaw-campus</t>
+          <t>Already watched by cra-dreu</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw campus site</t>
+          <t>CRA DREU</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -12744,24 +12782,24 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/</t>
+          <t>https://cra.org/cra-wp/dreu/</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: internships for 'undergraduate and graduate students'. The fellowship rows' campus.deshaw.com/fellowships URL now redirects here; this page is watched so a returning fellowship shows up.</t>
+          <t>Verified 2026-09-26: 'High school graduates who have been accepted ... are also eligible'; priority to CS majors. Large page (94K chars).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Already watched by digitaleconomy-careers</t>
+          <t>Already watched by cs-social-good-fellowships</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Stanford Digital Economy Lab student research assistant positions</t>
+          <t>CS+Social Good Summer Fellowships</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -12769,68 +12807,68 @@
           <t>Stanford-only</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>https://digitaleconomy.stanford.edu/about/careers-and-opportunities/</t>
+          <t>https://cardinalservice.stanford.edu/opportunities/cssocial-good-summer-fellowships</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'we offer a small number of opportunities for undergraduate and graduate students, primarily for current Stanford students ... Research assistant positions open periodically throughout the year'. On 2026-10-08: 'There are currently no open opportunities at the Lab, but this page will be updated when they become available.'</t>
+          <t>Verified 2026-09-30 from the 2026 SOLO listing: 'enrolled as a first-year, sophomore, or junior ... must have completed CS 106B by the end of Spring Quarter.' $7,000 base stipend, full-time summer with a tech-for-good partner. Cardinal Quarter.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Already watched by dimacs-reu</t>
+          <t>Already watched by curis</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>DIMACS REU</t>
+          <t>Stanford CURIS</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>https://dimacs.rutgers.edu/reu-main</t>
+          <t>https://curis.stanford.edu/</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'We do not usually admit freshmen' - watch for sophomore year.</t>
+          <t>CS dept paid summer research. Project list posted late Jan. Also lists year-round projects for units or hourly pay. | Checked 2026-09-26: now watched with render_js - the page is client-rendered and yields 1,264 chars in the browser.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Already watched by dukequant-competition</t>
+          <t>Already watched by datasurf</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Duke FinTech Trading Competition</t>
+          <t>Stanford DataSURF (formerly SURP-Stats)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -12840,120 +12878,120 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>https://www.duke.edu/</t>
+          <t>https://datasciencemajor.stanford.edu/research-impact/data-science-undergraduate-research-focus</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>3 months, paper trading, bracket format. Sponsors include Schonfeld. Lowest time commitment. | Checked 2026-09-26: Duke Quantitative Finance's competition page is dukequant.com/general-7 (watched with render_js); not yet confirmed to be the same event this row names. The listed duke.edu is kept.</t>
+          <t>Verified 2026-09-30: 'Stanford undergraduate students from any department who meet the prerequisites are encouraged to apply' (examples: STATS 60, MATH 51-53, CS 106A/B). 10 weeks, $8,500 stipend plus need-based supplement.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Already watched by evercore-campus</t>
+          <t>Already watched by deshaw-campus</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Evercore student events</t>
+          <t>D. E. Shaw Nexus Fellowship</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>https://evercore.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Oleeo Atom feed, 39 entries; vacancy/1/feed has 29 more. Some events are restricted-audience per the Simplify blog.</t>
+          <t>THE one for a first-year to target the following year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging. | Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Already watched by futureforce-launchpad</t>
+          <t>Already watched by deshaw-campus</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Salesforce Futureforce Tech Launchpad (CodePath)</t>
+          <t>D. E. Shaw campus site</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>https://info.codepath.org/futureforce-tech-launchpad</t>
+          <t>https://campus.deshaw.com/</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Students who will complete their sophomore year in Spring 2026' - so summer 2028 for a class of 2030.</t>
+          <t>Verified 2026-09-26: internships for 'undergraduate and graduate students'. The fellowship rows' campus.deshaw.com/fellowships URL now redirects here; this page is watched so a returning fellowship shows up.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hackgt</t>
+          <t>Already watched by dimacs-reu</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>HackGT</t>
+          <t>DIMACS REU</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>https://hack.gt/</t>
+          <t>https://dimacs.rutgers.edu/reu-main</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08 (rendered page): 'If you will be traveling from afar, we offer reimbursements to GT'; the page links a travel guide.</t>
+          <t>Verified 2026-09-26: 'We do not usually admit freshmen' - watch for sophomore year.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hackprinceton</t>
+          <t>Already watched by dukequant-competition</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>HackPrinceton</t>
+          <t>Duke FinTech Trading Competition</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12961,36 +12999,36 @@
           <t>Competition</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>https://www.hackprinceton.com/</t>
+          <t>https://www.duke.edu/</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'Applicants must be matriculated in an undergraduate or graduate program at a college or university.' Travel: 'Some admitted hackers may receive a travel stipend that covers part of their travel expenses.' No cost to apply or attend.</t>
+          <t>3 months, paper trading, bracket format. Sponsors include Schonfeld. Lowest time commitment. | Checked 2026-09-26: Duke Quantitative Finance's competition page is dukequant.com/general-7 (watched with render_js); not yet confirmed to be the same event this row names. The listed duke.edu is kept.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hackumass</t>
+          <t>Already watched by evercore-campus</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>HackUMass</t>
+          <t>Evercore student events</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -13000,61 +13038,61 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>https://www.hackumass.com/</t>
+          <t>https://evercore.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'HackUMass XIV is open to ALL college students, including graduate students, regardless of major!' Travel: 'If you apply by the early application deadline, you have the opportunity to apply for travel reimbursement.' Early applications for XIV were already closed on 2026-10-08.</t>
+          <t>Verified 2026-09-26: Oleeo Atom feed, 39 entries; vacancy/1/feed has 29 more. Some events are restricted-audience per the Simplify blog.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hai-research-opportunities</t>
+          <t>Already watched by futureforce-launchpad</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Stanford HAI student research assistant positions</t>
+          <t>Salesforce Futureforce Tech Launchpad (CodePath)</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>https://hai.stanford.edu/research/research-opportunities</t>
+          <t>https://info.codepath.org/futureforce-tech-launchpad</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'HAI ... is looking for research assistants ... Please note that the position is open to Stanford students ONLY.' No class year stated. Openings listed by centre: Digital Economy Lab (data gathering, cleaning and analysis; 'Proficiency with R or Python is required'), CRFM ('strong students with engineering/CS expertise to build CRFM infrastructure (e.g. the HELM benchmark)'), and HAI programmes. Apply links are not in the static page.</t>
+          <t>Verified 2026-09-26: 'Students who will complete their sophomore year in Spring 2026' - so summer 2028 for a class of 2030.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Already watched by harvard-undergraduate-trading</t>
+          <t>Already watched by generalatlantic-greenhouse</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Harvard Undergraduate Trading Competition</t>
+          <t>General Atlantic careers board</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Finance program</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -13064,29 +13102,29 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>https://www.huqt.com/</t>
+          <t>https://job-boards.greenhouse.io/generalatlantic</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate intercollegiate trading competition run by Harvard Undergraduate Quantitative Traders. The organisation rebranded: the article's link harvarduqt.com/competition 301-redirects to www.huqt.com/competition, which 404s. The live site is huqt.com and it has an Apply link. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year and team format not published - verify before planning.</t>
+          <t>Growth equity. Greenhouse board linked from generalatlantic.com/careers, 12 postings on 2026-10-11.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hedgewest-sf-meetup-series</t>
+          <t>Already watched by guggenheim-campus-workday</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>HedgeWest SF Meetup Series</t>
+          <t>Guggenheim Securities campus board</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Finance program</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -13096,24 +13134,24 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>https://hedgewestsf.org/</t>
+          <t>https://guggenheim.wd1.myworkdayjobs.com/Guggenheim_Careers_Campus</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Quant/hedge-fund meetup series in San Francisco - one of the very few items in this article that is geographically local to Stanford. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify whether undergraduates may attend.</t>
+          <t>Linked from guggenheimsecurities.com/careers. Its Freshman Day on the Job and Sophomore FOCUS are described as 'geared towards individuals who have demonstrated resilience and excellence under challenging circumstances' (hardship-targeted). The board also carries its general summer analyst roles. Guggenheim_Undergraduate_Programs had 0 postings on 2026-10-11.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hfac-citadel-pitch</t>
+          <t>Already watched by hackgt</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>HFAC x Citadel Intercollegiate Stock Pitch Competition</t>
+          <t>HackGT</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -13121,31 +13159,31 @@
           <t>Competition</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>https://www.harvardfac.org/hfac-citadel-pitch-comp</t>
+          <t>https://hack.gt/</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08 on the official page: HFAC with the Citadel Associate Program "is pleased to invite current sophomores, juniors, and seniors"; "*Eligibility: Teams of 2-4 undergraduate students in good standing, eighteen years of age or older, graduating between December 2026 and May 2029, attending a university located in the 50 US States, US territories, Washington, DC, or Canada". The 2026 window excludes a 2030 graduate. "Citadel will sponsor travel and lodging for all selected teams", and "all finalists in the sophomore class (Class of 2029) will receive a first round interview with the Citadel Associate Program." The page URL is not year-specific, so the 2027 edition, whose window should include the class of 2030 as sophomores, is expected here.</t>
+          <t>Verified 2026-10-08 (rendered page): 'If you will be traveling from afar, we offer reimbursements to GT'; the page links a travel guide.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hophacks</t>
+          <t>Already watched by hackprinceton</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>HopHacks</t>
+          <t>HackPrinceton</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -13160,24 +13198,24 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>https://hophacks.com/</t>
+          <t>https://www.hackprinceton.com/</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'We will not be offering individual travel reimbursements. However, please see the busing interest form ... If enough people from your city sign up, we may send a FREE bus.'</t>
+          <t>Verified 2026-10-08: 'Applicants must be matriculated in an undergraduate or graduate program at a college or university.' Travel: 'Some admitted hackers may receive a travel stipend that covers part of their travel expenses.' No cost to apply or attend.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Already watched by iaqf-academic-paper-competition</t>
+          <t>Already watched by hackumass</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>IAQF Academic Paper Competition</t>
+          <t>HackUMass</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -13192,29 +13230,29 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>https://www.iaqf.org/upcoming-events</t>
+          <t>https://www.hackumass.com/</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>International Association for Quantitative Finance paper competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. A paper is a slower but more durable credential than a trading competition; verify undergraduate eligibility.</t>
+          <t>Verified 2026-10-08: 'HackUMass XIV is open to ALL college students, including graduate students, regardless of major!' Travel: 'If you apply by the early application deadline, you have the opportunity to apply for travel reimbursement.' Early applications for XIV were already closed on 2026-10-08.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Already watched by icerm-summer</t>
+          <t>Already watched by hai-research-opportunities</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Summer@ICERM</t>
+          <t>Stanford HAI student research assistant positions</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -13224,61 +13262,61 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>https://icerm.brown.edu/summerug/</t>
+          <t>https://hai.stanford.edu/research/research-opportunities</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Applicants must be matriculating undergraduate students'.</t>
+          <t>Verified 2026-10-08: 'HAI ... is looking for research assistants ... Please note that the position is open to Stanford students ONLY.' No class year stated. Openings listed by centre: Digital Economy Lab (data gathering, cleaning and analysis; 'Proficiency with R or Python is required'), CRFM ('strong students with engineering/CS expertise to build CRFM infrastructure (e.g. the HELM benchmark)'), and HAI programmes. Apply links are not in the static page.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Already watched by icpc-pnw</t>
+          <t>Already watched by harriswilliams-summer-analyst</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>ICPC</t>
+          <t>Harris Williams Summer Analyst</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Finance program</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>https://icpc.global/</t>
+          <t>https://www.harriswilliams.com/careers/summer-analyst</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: icpc.global is a JavaScript shell (53 chars); Stanford's regional, pnw.na.icpc.global, is what is watched.</t>
+          <t>Page (2026-10-11): 'Applications typically open during the late fall semester of your sophomore year.' Extern lists an Oct 2026-Jan 2027 window for Summer 2028.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Already watched by imc-launchpad-us</t>
+          <t>Already watched by harriswilliams-workday</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>IMC Launchpad (US)</t>
+          <t>Harris Williams careers board</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Finance program</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -13288,61 +13326,61 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
+          <t>https://pnc.wd5.myworkdayjobs.com/HarrisWilliams</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>IMC's US student program - distinct from the EU Business Course and UK Masterclass, which are geography-excluded. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year not published; verify.</t>
+          <t>Harris Williams's Workday board (on the PNC tenant), linked from its Summer Analyst page. 18 postings on 2026-10-11.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Already watched by imc-prosperity</t>
+          <t>Already watched by harvard-undergraduate-trading</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>IMC Prosperity Trading Competition</t>
+          <t>Harvard Undergraduate Trading Competition</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>https://prosperity.imc.com/</t>
+          <t>https://www.huqt.com/</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Teams up to 5, $50,000 pool, fully online. Most accessible serious quant competition. Stanford won top-US in year one.</t>
+          <t>Undergraduate intercollegiate trading competition run by Harvard Undergraduate Quantitative Traders. The organisation rebranded: the article's link harvarduqt.com/competition 301-redirects to www.huqt.com/competition, which 404s. The live site is huqt.com and it has an Apply link. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year and team format not published - verify before planning.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Already watched by ipam-rips</t>
+          <t>Already watched by hedgewest-sf-meetup-series</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>IPAM RIPS (UCLA)</t>
+          <t>HedgeWest SF Meetup Series</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -13352,61 +13390,61 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>https://www.ipam.ucla.edu/programs/student-research-programs/</t>
+          <t>https://hedgewestsf.org/</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Research in Industrial Projects for Students: teams of undergraduates on sponsored industry problems in applied mathematics.</t>
+          <t>Quant/hedge-fund meetup series in San Francisco - one of the very few items in this article that is geographically local to Stanford. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify whether undergraduates may attend.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-fttp</t>
+          <t>Already watched by hfac-citadel-pitch</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Jane Street FTTP</t>
+          <t>HFAC x Citadel Intercollegiate Stock Pitch Competition</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
+          <t>https://www.harvardfac.org/hfac-citadel-pitch-comp</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Classes + team-based mock trading. STEM majors, no finance background needed. Rolling - apply week one.</t>
+          <t>Verified 2026-10-08 on the official page: HFAC with the Citadel Associate Program "is pleased to invite current sophomores, juniors, and seniors"; "*Eligibility: Teams of 2-4 undergraduate students in good standing, eighteen years of age or older, graduating between December 2026 and May 2029, attending a university located in the 50 US States, US territories, Washington, DC, or Canada". The 2026 window excludes a 2030 graduate. "Citadel will sponsor travel and lodging for all selected teams", and "all finalists in the sophomore class (Class of 2029) will receive a first round interview with the Citadel Associate Program." The page URL is not year-specific, so the 2027 edition, whose window should include the class of 2030 as sophomores, is expected here.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-preview</t>
+          <t>Already watched by hophacks</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Preview</t>
+          <t>HopHacks</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -13416,93 +13454,93 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/preview/</t>
+          <t>https://hophacks.com/</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26 (source research): day-long programme 'for students at any point in their academic career'. One of the 12 programmes on the watched janestreet-programs index; this watches its own page.</t>
+          <t>Verified 2026-10-08: 'We will not be offering individual travel reimbursements. However, please see the busing interest form ... If enough people from your city sign up, we may send a FREE bus.'</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by iaqf-academic-paper-competition</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Jane Street AMP - TA role</t>
+          <t>IAQF Academic Paper Competition</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/amp/</t>
+          <t>https://www.iaqf.org/upcoming-events</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Paid Jane Street summer on the teaching side. Housing, meals, travel covered. Eligible from spring 2027.</t>
+          <t>International Association for Quantitative Finance paper competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. A paper is a slower but more durable credential than a trading competition; verify undergraduate eligibility.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by icerm-summer</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Jane Street ETC</t>
+          <t>Summer@ICERM</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>INVITE</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://icerm.brown.edu/summerug/</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Electronic Trading Challenge. Entry via university, prior JS events, or the puzzle ecosystem.</t>
+          <t>Verified 2026-09-26: 'Applicants must be matriculating undergraduate students'.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by icpc-pnw</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Jane Street SEE</t>
+          <t>ICPC</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -13512,24 +13550,24 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://icpc.global/</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Software Engineering Experience - OCaml and systems design.</t>
+          <t>Checked 2026-09-26: icpc.global is a JavaScript shell (53 chars); Stanford's regional, pnw.na.icpc.global, is what is watched.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by imc-launchpad-us</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Symposium</t>
+          <t>IMC Launchpad (US)</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -13539,25 +13577,29 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>INVITE</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr"/>
+          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>IMC's US student program - distinct from the EU Business Course and UK Masterclass, which are geography-excluded. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year not published; verify.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by imc-prosperity</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Unboxed</t>
+          <t>IMC Prosperity Trading Competition</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -13565,32 +13607,36 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr"/>
+          <t>https://prosperity.imc.com/</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Teams up to 5, $50,000 pool, fully online. Most accessible serious quant competition. Stanford won top-US in year one.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jefferies-campus</t>
+          <t>Already watched by insightpartners-ashby</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Jefferies campus opportunities</t>
+          <t>Insight Partners job board</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Finance program</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -13600,61 +13646,61 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>https://jefferies.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
+          <t>https://jobs.ashbyhq.com/insight-partners</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Oleeo Atom feed, 60 entries. Banking is lower priority than quant.</t>
+          <t>Insight Partners' own Ashby board, linked from its Summer Analyst page. Zero postings on 2026-10-11 (2027 cycle closed).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jhuapl-internships</t>
+          <t>Already watched by insightpartners-campus</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Johns Hopkins APL internships</t>
+          <t>Insight Partners Summer Investment Analyst</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Finance program</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>https://www.jhuapl.edu/careers/internships</t>
+          <t>https://info.insightpartners.com/Campus-Recruiting-Programs.html</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Page states a minimum GPA requirement. Simplify already carries some APL postings; this watches the programme page itself.</t>
+          <t>VC/growth equity. Page (2026-10-11): 'Undergraduate or 5th-year Master's students graduating between December 2028-June 2029 are eligible to apply to our 2028 Summer Investment Analyst Program.' A class-of-2030 student fits the 2029 cycle. Freshmen are pointed at the Campus Recruiting Talent Pool.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jpmc-career-edyou</t>
+          <t>Already watched by insightpartners-summer-analyst</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>JPMorganChase Career.edYOU Academy</t>
+          <t>Insight Partners Summer Analyst page</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Finance program</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -13664,56 +13710,56 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/career-edyou</t>
+          <t>https://info.insightpartners.com/Summer-Analyst-Program.html</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'designed for college sophomores studying in the United States'.</t>
+          <t>The programme's own page; links its Ashby postings. Said 'no longer accepting applications' for 2027 on 2026-10-11.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jpmc-fellowship</t>
+          <t>Already watched by ipam-rips</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>JPMC Fellowship Program</t>
+          <t>IPAM RIPS (UCLA)</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/jpmcfellowship</t>
+          <t>https://www.ipam.ucla.edu/programs/student-research-programs/</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'sophomore students, including, without limitation, Black, Hispanic and Latino... All sophomore students... regardless of background, are welcome'.</t>
+          <t>Research in Industrial Projects for Students: teams of undergraduates on sponsored industry problems in applied mathematics.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jumptrading-greenhouse</t>
+          <t>Already watched by janestreet-fttp</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Jump Trading Campus Jump Early Access</t>
+          <t>Jane Street FTTP</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -13728,29 +13774,29 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>https://www.jumptrading.com/hr/students-new-grads</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30 from the 2026 posting: 'First-year undergraduates at US universities' in math/CS/physics/stats/engineering/econ. One-day programme in Chicago, travel/meals/lodging covered. Posts on the Greenhouse board watched by jumptrading-greenhouse; not live today.</t>
+          <t>Classes + team-based mock trading. STEM majors, no finance background needed. Rolling - apply week one.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Already watched by kingcenter-summer-rf</t>
+          <t>Already watched by janestreet-preview</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>King Center Summer Undergraduate Research Fellows</t>
+          <t>Jane Street Preview</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -13760,24 +13806,24 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>https://kingcenter.stanford.edu/opportunities/undergraduate-students/summer-full-time-undergraduate-research-fellow-program</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/preview/</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'The program is open to matriculated Stanford undergraduates who will be registered in the autumn quarter following the fellowship.' Full-time summer research on development-economics faculty projects. 'Stipend: $8,500.' 'Summer 2027 opportunities will be posted in February 2027 and the deadline to apply will be in late Winter 2027.'</t>
+          <t>Verified 2026-09-26 (source research): day-long programme 'for students at any point in their academic career'. One of the 12 programmes on the watched janestreet-programs index; this watches its own page.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Already watched by kkr-greenhouse</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>KKR Scholars Program</t>
+          <t>Jane Street AMP - TA role</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -13785,132 +13831,128 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>https://www.kkr.com/careers/student-careers/student-career-opportunities</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/amp/</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2025 posting: 'rising sophomores graduating with a Bachelor's degree in December 2027 – June 2028'. The 2027 edition should be Dec 2029-Jun 2030, the owner's window. Late-May dates may clash with Stanford spring quarter. Posts on KKR's Greenhouse board, slug 'staged'.</t>
+          <t>Paid Jane Street summer on the teaching side. Housing, meals, travel covered. Eligible from spring 2027.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Already watched by kleinerperkins-fellows-ashby</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Kleiner Perkins Engineering Fellows</t>
+          <t>Jane Street ETC</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>INVITE</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>https://www.kleinerperkins.com/fellows/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30 from the Ashby posting: no class-year gate; wants 'Degree in computer science, engineering, math, physics or other fields related to software engineering' and Bay Area availability. Summer placement at a KP portfolio startup plus speaker series. Selective, and cohorts skew upperclass.</t>
+          <t>Electronic Trading Challenge. Entry via university, prior JS events, or the puzzle ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Already watched by lahacks</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>LA Hacks</t>
+          <t>Jane Street SEE</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>https://www.lahacks.com/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'LA Hacks is open to college students of all skill levels'; 'hosted at UCLA's Pauley Pavilion ... in Mid-April 2027'. The FAQ has a 'Travel Reimbursement' tab, but its answer is not in the served HTML, so whether travel is reimbursed for 2027 is unverified.</t>
+          <t>Software Engineering Experience - OCaml and systems design.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Already watched by lanl-students</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>LANL student internships (Los Alamos National Laboratory)</t>
+          <t>Jane Street Symposium</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>INVITE</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>https://www.lanl.gov/engage/collaboration/internships</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>Lab-run undergraduate internship programme. The old /careers/career-options/student-internships URL redirects here.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Already watched by llnl-students</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>LLNL student internships (Lawrence Livermore National Laboratory)</t>
+          <t>Jane Street Unboxed</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -13920,153 +13962,153 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>https://www.llnl.gov/join-our-team/careers/student-internship-veteran-programs</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>Undergraduate summer internships plus internally and externally sponsored student programmes. Not part of DOE SULI's lab list in this file.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Already watched by luisae</t>
+          <t>Already watched by jefferies-campus</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>LuisaE/opportunities</t>
+          <t>Jefferies campus opportunities</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/LuisaE/opportunities</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr"/>
+          <t>https://jefferies.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-26: Oleeo Atom feed, 60 entries. Banking is lower priority than quant.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Already watched by math-drp</t>
+          <t>Already watched by jhuapl-internships</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Stanford Directed Reading Program (math)</t>
+          <t>Johns Hopkins APL internships</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>https://mathdrp.stanford.edu/</t>
+          <t>https://www.jhuapl.edu/careers/internships</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Quarter with a grad-student mentor, ends in a colloquium talk. Near-zero barrier and the cheapest route to a SURIM letter. | Corrected 2026-10-08: website was the department homepage https://mathematics.stanford.edu/; the programme's own site is https://mathdrp.stanford.edu/, now watched by math-drp. 'We welcome applications from all Stanford undergraduates interested in mathematics'; one application per quarter (Fall 2026 was due Monday September 28).</t>
+          <t>Page states a minimum GPA requirement. Simplify already carries some APL postings; this watches the programme page itself.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mathprograms-listing</t>
+          <t>Already watched by jpmc-career-edyou</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>MathPrograms.org programme listing</t>
+          <t>JPMorganChase Career.edYOU Academy</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>https://www.mathprograms.org/db/program</t>
+          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/career-edyou</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: AMS-run application portal most math REUs use (UChicago, PCMI, Polymath Jr); already lists POLYMATHREU2027 and SLMath PROOF 2027. Substitutes for the NSF REU directory (AWS WAF challenge) and the AMS REU list (403), neither readable by this client.</t>
+          <t>Verified 2026-09-26: 'designed for college sophomores studying in the United States'.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Already watched by meta-hacker-cup</t>
+          <t>Already watched by jpmc-fellowship</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Meta Hacker Cup</t>
+          <t>JPMC Fellowship Program</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/codingcompetitions/hacker-cup</t>
+          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/jpmcfellowship</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Open to participants around the world'. Page still shows the 2025 season. JavaScript page: 15 chars plain, 1,485 rendered.</t>
+          <t>Verified 2026-09-26: 'sophomore students, including, without limitation, Black, Hispanic and Latino... All sophomore students... regardless of background, are welcome'.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Already watched by miami-stock-pitch</t>
+          <t>Already watched by jpmc-students</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Miami University - Cleveland Research Intercollegiate Stock Pitch Competition</t>
+          <t>JPMorganChase student programs</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Finance program</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -14076,24 +14118,24 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>https://miamioh.edu/fsb/departments/finance/stock-pitch.html</t>
+          <t>https://www.jpmorganchase.com/careers/explore-opportunities/students-and-graduates</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08 on the official page, which still describes the 2026 edition: "Each team of 2-4 students will assemble a slide deck to pitch a long or short equity position with a 3-12 month horizon." "interested teams must register by the end of the day on March 6"; non-Miami teams submit a written proposal (max 20 slides) by Mar 25; finalists attend a dinner Apr 9 and present in person Apr 10 in Oxford, OH, judged by Cleveland Research Company. Prizes $1,500 / $1,000 / $500. No class-year restriction stated on the page.</t>
+          <t>Page (2026-10-11): 'Pre-internship events range from one day to a few weeks and are meant for college freshman, sophomores and juniors.' Covers Code for Good, Inside the Industry, Find Your Fit and the AWM Challenge named on Simplify's list.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Already watched by millennium-eightfold</t>
+          <t>Already watched by jumptrading-greenhouse</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Meet Millennium</t>
+          <t>Jump Trading Campus Jump Early Access</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -14101,36 +14143,36 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>https://www.mlp.com/life-at-millennium/inside-meet-millennium/</t>
+          <t>https://www.jumptrading.com/hr/students-new-grads</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'high-performing undergraduate and master's students ... Designed as an insight into Millennium's 2027 Summer Intern Program'. Travel to one of five offices; SWE/quant-engineering simulations. www.mlp.com is WP Engine, so not watched directly; the posting should surface via millennium-eightfold.</t>
+          <t>Verified 2026-09-30 from the 2026 posting: 'First-year undergraduates at US universities' in math/CS/physics/stats/engineering/econ. One-day programme in Chicago, travel/meals/lodging covered. Posts on the Greenhouse board watched by jumptrading-greenhouse; not live today.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mit-battlecode-2027</t>
+          <t>Already watched by kingcenter-summer-rf</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>MIT Battlecode 2027</t>
+          <t>King Center Summer Undergraduate Research Fellows</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -14140,29 +14182,29 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>https://battlecode.org/</t>
+          <t>https://kingcenter.stanford.edu/opportunities/undergraduate-students/summer-full-time-undergraduate-research-fellow-program</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>MIT's real-time strategy AI competition: you write an autonomous player that commands a robot army, then compete in scrimmages and bracketed tournaments over January. Over $20,000 in total prize money. Open beyond MIT - 'Anyone can write a bot, create a team, and participate in scrimmage matches/rankings.' Prize-tournament gates from the Full Eligibility Rules (battlecode.org/about.html): Sprint Tournaments - 'All teams are eligible.' US Qualifier - 'Teams must consist entirely of US college students studying full-time, or in a transition phase.' Final Tournament - 'Teams must have qualified via the US or International Qualifier.' MIT Newbie Tournament is MIT-only and High School Tournament is high-school-only, so neither applies. Unlike MIT Pokerbots, no MIT-affiliated teammate or MIT certificate is needed for the track you would enter. As of Sep 2026 the site still reads 'Battlecode 2026 ended on January 31st, 2026!' - no 2027 registration date posted yet, though the page already references Battlecode 2027 sponsorships. No team size limit, age limit, or citizenship rule beyond 'US college student' was stated on the pages read. Source: battlecode.org home page and about.html.</t>
+          <t>Verified 2026-10-08: 'The program is open to matriculated Stanford undergraduates who will be registered in the autumn quarter following the fellowship.' Full-time summer research on development-economics faculty projects. 'Stipend: $8,500.' 'Summer 2027 opportunities will be posted in February 2027 and the deadline to apply will be in late Winter 2027.'</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mit-trading-competition</t>
+          <t>Already watched by kkr-greenhouse</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Traders@MIT Trading Competition</t>
+          <t>KKR Scholars Program</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -14172,29 +14214,29 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>https://traders.mit.edu/competition</t>
+          <t>https://www.kkr.com/careers/student-careers/student-career-opportunities</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Largest intercollegiate competition, $20,000+. NOT the same as Pokerbots - this one IS open to first-years.</t>
+          <t>2025 posting: 'rising sophomores graduating with a Bachelor's degree in December 2027 – June 2028'. The 2027 edition should be Dec 2029-Jun 2030, the owner's window. Late-May dates may clash with Stanford spring quarter. Posts on KKR's Greenhouse board, slug 'staged'.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mitll-students</t>
+          <t>Already watched by kleinerperkins-fellows-ashby</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>MIT Lincoln Laboratory student opportunities</t>
+          <t>Kleiner Perkins Engineering Fellows</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -14204,61 +14246,61 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>https://www.ll.mit.edu/careers/student-opportunities</t>
+          <t>https://www.kleinerperkins.com/fellows/</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Several tracks. The industry-mentor programme is for students in their junior year; the Summer Research Program takes undergraduate and graduate students.</t>
+          <t>Verified 2026-09-30 from the Ashby posting: no class-year gate; wants 'Degree in computer science, engineering, math, physics or other fields related to software engineering' and Bay Area availability. Summer placement at a KP portfolio startup plus speaker series. Selective, and cohorts skew upperclass.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mlh-season-events</t>
+          <t>Already watched by lahacks</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>MLH hackathon season calendar</t>
+          <t>LA Hacks</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>https://www.mlh.com/seasons/2027/events</t>
+          <t>https://www.lahacks.com/</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: MLH's official season calendar (e.g. Gator Quant Hacks, MHacks, Oct 2026). Too high-churn for page_text; treat as a manual/calendar pointer. Correction 2026-10-08: now watched as page_text (source mlh-season-events); one Change per day at most, so the churn is bounded.</t>
+          <t>Verified 2026-10-08: 'LA Hacks is open to college students of all skill levels'; 'hosted at UCLA's Pauley Pavilion ... in Mid-April 2027'. The FAQ has a 'Travel Reimbursement' tab, but its answer is not in the served HTML, so whether travel is reimbursed for 2027 is unverified.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Already watched by msande-ay-reu</t>
+          <t>Already watched by lanl-students</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Stanford MS&amp;E Academic-Year REU</t>
+          <t>LANL student internships (Los Alamos National Laboratory)</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -14268,29 +14310,29 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>https://msandepro.stanford.edu/academic-year-research-experience-undergraduates</t>
+          <t>https://www.lanl.gov/engage/collaboration/internships</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'research opportunities to students from any STEM-inclined major at Stanford during the academic year (Fall, Winter, and Spring quarters)'. Paired with an MS&amp;E faculty or PhD mentor for independent-study course credit, not pay. 'The application for the REU (Academic Year) is typically open a few weeks prior to each quarter and the deadline would be the night before the first day of the quarter.'</t>
+          <t>Lab-run undergraduate internship programme. The old /careers/career-options/student-internships URL redirects here.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Already watched by msande-reu</t>
+          <t>Already watched by lincoln-greenhouse</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Stanford MS&amp;E Summer REU</t>
+          <t>Lincoln International careers board</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Finance program</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -14300,24 +14342,24 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>https://msande.stanford.edu/research-impact/mse-student-research/research-experience-undergraduates</t>
+          <t>https://job-boards.greenhouse.io/lincolninternational</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'current Stanford undergraduate students are matched with participating MS&amp;E faculty members and PhD students'; no class year stated. '10 weeks of research', paid full time. 'Applications for the summer REU program are available each year between January 15 and February 15, with the goal of matching students to faculty mentors by mid-March.' Application form requires a Stanford login.</t>
+          <t>Simplify's underclassmen finance list names a Lincoln International Sophomore Job Shadow Program. Its Greenhouse board had 41 postings on 2026-10-11, including 2027 summer analyst roles.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Already watched by nist-surf</t>
+          <t>Already watched by llnl-students</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>NIST SURF</t>
+          <t>LLNL student internships (Lawrence Livermore National Laboratory)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -14325,100 +14367,96 @@
           <t>Research / math</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/surf</t>
+          <t>https://www.llnl.gov/join-our-team/careers/student-internship-veteran-programs</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'only open to U.S. citizens and U.S. permanent residents enrolled as undergraduate students at U.S. colleges or universities'; states no class-year minimum. 11 weeks, $710/week plus lodging/travel allowance. Information Technology Lab has math/CS/ML projects.</t>
+          <t>Undergraduate summer internships plus internally and externally sponsored student programmes. Not part of DOE SULI's lab list in this file.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Already watched by nsa-students</t>
+          <t>Already watched by luisae</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>NSA student programs</t>
+          <t>LuisaE/opportunities</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>USE</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>https://www.intelligencecareers.gov/nsa/students</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>NSA's student internship and co-op listings on intelligencecareers.gov. Security clearance means US citizens only.</t>
-        </is>
-      </c>
+          <t>https://github.com/LuisaE/opportunities</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Already watched by nuft-2027</t>
+          <t>Already watched by math-drp</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>NUFT 2027 Quant Internships</t>
+          <t>Stanford Directed Reading Program (math)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>USE WEEKLY</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/northwesternfintech/2027QuantInternships</t>
+          <t>https://mathdrp.stanford.edu/</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>47 firms. No class-year tags - use as a firm checklist and open each careers page yourself.</t>
+          <t>Quarter with a grad-student mentor, ends in a colloquium talk. Near-zero barrier and the cheapest route to a SURIM letter. | Corrected 2026-10-08: website was the department homepage https://mathematics.stanford.edu/; the programme's own site is https://mathdrp.stanford.edu/, now watched by math-drp. 'We welcome applications from all Stanford undergraduates interested in mathematics'; one application per quarter (Fall 2026 was due Monday September 28).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Already watched by open-source-quantitative-finance</t>
+          <t>Already watched by mathprograms-listing</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Open Source Quantitative Finance Conference</t>
+          <t>MathPrograms.org programme listing</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -14428,29 +14466,29 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>https://osqf.org/</t>
+          <t>https://www.mathprograms.org/db/program</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
+          <t>Verified 2026-09-26: AMS-run application portal most math REUs use (UChicago, PCMI, Polymath Jr); already lists POLYMATHREU2027 and SLMath PROOF 2027. Substitutes for the NSF REU directory (AWS WAF challenge) and the AMS REU list (403), neither readable by this client.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Already watched by optiver-futurefocus</t>
+          <t>Already watched by meta-hacker-cup</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Optiver FutureFocus Chicago 2026</t>
+          <t>Meta Hacker Cup</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -14460,29 +14498,29 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
+          <t>https://www.facebook.com/codingcompetitions/hacker-cup</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Verified 2026-09-26: 'Open to participants around the world'. Page still shows the 2025 season. JavaScript page: 15 chars plain, 1,485 rendered.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Already watched by optiver-ready-trader</t>
+          <t>Already watched by miami-stock-pitch</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Optiver Ready Trader Go</t>
+          <t>Miami University - Cleveland Research Intercollegiate Stock Pitch Competition</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -14492,25 +14530,29 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="F80" s="3" t="inlineStr"/>
+          <t>https://miamioh.edu/fsb/departments/finance/stock-pitch.html</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-10-08 on the official page, which still describes the 2026 edition: "Each team of 2-4 students will assemble a slide deck to pitch a long or short equity position with a 3-12 month horizon." "interested teams must register by the end of the day on March 6"; non-Miami teams submit a written proposal (max 20 slides) by Mar 25; finalists attend a dinner Apr 9 and present in person Apr 10 in Oxford, OH, judged by Cleveland Research Company. Prizes $1,500 / $1,000 / $500. No class-year restriction stated on the page.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Already watched by physics-surp</t>
+          <t>Already watched by millennium-eightfold</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Stanford Physics / Applied Physics / SLAC Summer Research Program</t>
+          <t>Meet Millennium</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -14520,24 +14562,24 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>https://physics.stanford.edu/undergraduate/undergraduate-research</t>
+          <t>https://www.mlp.com/life-at-millennium/inside-meet-millennium/</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'We accept applications from current freshmen, sophomores, and juniors.' Gate: Fellowships go to 'Stanford undergraduate Physics and Engineering Physics majors, plus undeclared first-year students who are considering Physics/Engineering Physics as a major'. 'For beginning students, research experience is not required.' Base stipend $8,500 plus need-based supplement up to $1,500, ten weeks. Applicant finds a faculty mentor; 2026 Part 1 was due noon Jan 16, Part 2 Feb 20.</t>
+          <t>Verified 2026-09-30: 'high-performing undergraduate and master's students ... Designed as an insight into Millennium's 2027 Summer Intern Program'. Travel to one of five offices; SWE/quant-engineering simulations. www.mlp.com is WP Engine, so not watched directly; the posting should surface via millennium-eightfold.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Already watched by princeton-stock-pitch</t>
+          <t>Already watched by mit-battlecode-2027</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Princeton Stock Pitch (Tiger Investments)</t>
+          <t>MIT Battlecode 2027</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -14547,190 +14589,194 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>VIA CLUB</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>https://princetonstockpitch.vercel.app/</t>
+          <t>https://battlecode.org/</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08 on the official page: "open to student investment clubs nationwide"; "Who can enter: Open to all student investment clubs. Teams of 3-5 members." Free, virtual; 3-5 page memo, presentation and model on one long or short idea over $2B market cap. Tentative 2027 dates: submissions Mar 5, finalists Mar 12, live Zoom finals Mar 15. Prize pool ~$6,000. Entry is through a club, so a Stanford investing club team is the route in; no class-year restriction stated.</t>
+          <t>MIT's real-time strategy AI competition: you write an autonomous player that commands a robot army, then compete in scrimmages and bracketed tournaments over January. Over $20,000 in total prize money. Open beyond MIT - 'Anyone can write a bot, create a team, and participate in scrimmage matches/rankings.' Prize-tournament gates from the Full Eligibility Rules (battlecode.org/about.html): Sprint Tournaments - 'All teams are eligible.' US Qualifier - 'Teams must consist entirely of US college students studying full-time, or in a transition phase.' Final Tournament - 'Teams must have qualified via the US or International Qualifier.' MIT Newbie Tournament is MIT-only and High School Tournament is high-school-only, so neither applies. Unlike MIT Pokerbots, no MIT-affiliated teammate or MIT certificate is needed for the track you would enter. As of Sep 2026 the site still reads 'Battlecode 2026 ended on January 31st, 2026!' - no 2027 registration date posted yet, though the page already references Battlecode 2027 sponsorships. No team size limit, age limit, or citizenship rule beyond 'US college student' was stated on the pages read. Source: battlecode.org home page and about.html.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Already watched by purdue-srop</t>
+          <t>Already watched by mit-trading-competition</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Purdue Summer Research Opportunities Program (SROP)</t>
+          <t>Traders@MIT Trading Competition</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>https://www.purdue.edu/academics/ogsps/ogrs/summer-research-opportunity-program/</t>
+          <t>https://traders.mit.edu/competition</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>Part of the Big Ten Academic Alliance SROP. Page states eligibility includes US citizens, permanent residents, refugees and asylees enrolled at a US institution; read the full criteria on the page.</t>
+          <t>Largest intercollegiate competition, $20,000+. NOT the same as Pokerbots - this one IS open to first-years.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Already watched by ramp-ashby</t>
+          <t>Already watched by mitll-students</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Ramp Emerging Talent</t>
+          <t>MIT Lincoln Laboratory student opportunities</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>https://ramp.com/emerging-talent</t>
+          <t>https://www.ll.mit.edu/careers/student-opportunities</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'For interns: anyone who will be registered in an accredited 4 year university post-internship.' Fintech SWE internships posted on Ashby 'ramp'.</t>
+          <t>Several tracks. The industry-mentor programme is for students in their junior year; the Summer Research Program takes undergraduate and graduate students.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Already watched by reufinder-freshmen</t>
+          <t>Already watched by mlh-season-events</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>REU Finder - freshman-eligible filter</t>
+          <t>MLH hackathon season calendar</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Tracker / resource</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>USE</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>https://reufinder.com/programs-for-freshmen/</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr"/>
+          <t>https://www.mlh.com/seasons/2027/events</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-30: MLH's official season calendar (e.g. Gator Quant Hacks, MHacks, Oct 2026). Too high-churn for page_text; treat as a manual/calendar pointer. Correction 2026-10-08: now watched as page_text (source mlh-season-events); one Change per day at most, so the churn is bounded.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Already watched by sandia-students</t>
+          <t>Already watched by moelis-campus</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Sandia National Laboratories student internships</t>
+          <t>Moelis campus board</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Finance program</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>https://www.sandia.gov/careers/careers/students-and-postdocs/</t>
+          <t>https://moelis-careers.tal.net/vx/mobile-0/candidate/jobboard/vacancy/1/feed</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate and graduate internships across Sandia's sites.</t>
+          <t>Moelis's tal.net campus board, linked from moelis.com/careers/explore-opportunities. Per Extern 2026-10-08, US Summer Analyst applications typically open in the December of sophomore year. Moelis Young Leaders is identity-targeted.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Already watched by scudem</t>
+          <t>Already watched by msande-ay-reu</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>SCUDEM XI 2026</t>
+          <t>Stanford MS&amp;E Academic-Year REU</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>https://www.contest.comap.com/scudem/index.html</t>
+          <t>https://msandepro.stanford.edu/academic-year-research-experience-undergraduates</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: COMAP's differential-equations modelling challenge. FAQ: 'open to teams of 3 undergraduate or high school students. Each team must have a coach (typically a faculty member or instructor).' Ends in a 10-minute video judged by at least 3 judges. Needs a faculty coach.</t>
+          <t>Verified 2026-10-08: 'research opportunities to students from any STEM-inclined major at Stanford during the academic year (Fall, Winter, and Spring quarters)'. Paired with an MS&amp;E faculty or PhD mentor for independent-study course credit, not pay. 'The application for the REU (Academic Year) is typically open a few weeks prior to each quarter and the deadline would be the night before the first day of the quarter.'</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Already watched by seo-tech</t>
+          <t>Already watched by msande-reu</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>SEO Tech Developer + First-Year Academy</t>
+          <t>Stanford MS&amp;E Summer REU</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -14740,189 +14786,189 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>https://tech.seo-usa.org/</t>
+          <t>https://msande.stanford.edu/research-impact/mse-student-research/research-experience-undergraduates</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Enrolled as a sophomore'; the Academy is for 'first-year college students'. Page says 'All are welcome to apply'; SEO is a diversity organisation, so confirm eligibility by hand.</t>
+          <t>Verified 2026-10-08: 'current Stanford undergraduate students are matched with participating MS&amp;E faculty members and PhD students'; no class year stated. '10 weeks of research', paid full time. 'Applications for the summer REU program are available each year between January 15 and February 15, with the goal of matching students to faculty mentors by mid-March.' Application form requires a Stanford login.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Already watched by sfhacks</t>
+          <t>Already watched by nist-surf</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>SF Hacks</t>
+          <t>NIST SURF</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>https://www.sfhacks.io/</t>
+          <t>https://www.nist.gov/surf</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'All students are welcome, from high school through university.' 'We are not offering travel reimbursements this year.' San Francisco.</t>
+          <t>Verified 2026-09-30: 'only open to U.S. citizens and U.S. permanent residents enrolled as undergraduate students at U.S. colleges or universities'; states no class-year minimum. 11 weeks, $710/week plus lodging/travel allowance. Information Technology Lab has math/CS/ML projects.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Already watched by sfi-ucr</t>
+          <t>Already watched by nomura-insight</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>SFI Undergraduate Complexity Research</t>
+          <t>Nomura Insight Programs</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Finance program</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>https://www.santafe.edu/engage/learn/programs/undergraduate-complexity-research</t>
+          <t>https://www.nomura.com/careers/early-careers/insight-programs/</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'for current undergraduate students. Prior research experience is not required'; 'return to this page in November 2026'.</t>
+          <t>Page (2026-10-11): 'You must be on track to graduate in 2028'. Its Women's Immersion and SEO Explore tracks are identity-targeted.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Already watched by siepr-ugrf-academic-year</t>
+          <t>Already watched by nsa-students</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>SIEPR Undergraduate Research Fellows (academic year)</t>
+          <t>NSA student programs</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>https://siepr.stanford.edu/programs/undergraduate-student-opportunities/undergraduate-research-fellows-program/academic-year</t>
+          <t>https://www.intelligencecareers.gov/nsa/students</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'UGRFs must be enrolled as full-time undergraduate students at Stanford.' SOLO's listing 'SIEPR Undergraduate Research Program AY 2026-2027' says Deadline: Rolling deadline, Open To: Freshman, Sophomore, Junior. Part-time RA on posted economic-policy faculty projects, paid via payroll 'for up to 15 hours a week'. Online application with current course list, resume and cover letter. 'Applications for 2026 Autumn quarter are now open'; the Autumn programme runs September 22 to December 4, 2026.</t>
+          <t>NSA's student internship and co-op listings on intelligencecareers.gov. Security clearance means US citizens only.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Already watched by siepr-ugrf-summer</t>
+          <t>Already watched by nuft-2027</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>SIEPR Summer Undergraduate Research Fellows</t>
+          <t>NUFT 2027 Quant Internships</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Tracker / resource</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>https://siepr.stanford.edu/programs/undergraduate-student-opportunities/undergraduate-research-fellows-program/siepr-summer</t>
+          <t>https://github.com/northwesternfintech/2027QuantInternships</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'Participants must be current Stanford undergraduates during the summer quarter.' 10 weeks, $8,500, economic-policy research RA with SIEPR faculty. | Checked 2026-10-08: page unchanged in substance; now watched by siepr-ugrf-summer.</t>
+          <t>47 firms. No class-year tags - use as a firm checklist and open each careers page yourself.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Already watched by simplify-2027</t>
+          <t>Already watched by open-source-quantitative-finance</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>SimplifyJobs Summer 2027 Internships</t>
+          <t>Open Source Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/SimplifyJobs/Summer2027-Internships</t>
+          <t>https://osqf.org/</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>613 roles, 94 quant, but no class-year tagging and almost all target penultimate-year students.</t>
+          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Already watched by sjhacks</t>
+          <t>Already watched by optiver-futurefocus</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>SJHacks</t>
+          <t>Optiver FutureFocus Chicago 2026</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -14932,29 +14978,29 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>https://www.sjhacks.com/</t>
+          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'SJHacks is a 24-hour in-person hackathon at San Jose State University'; 2026 edition April 25-26 at Guildhouse, San Jose. The page states no eligibility rule and nothing about travel.</t>
+          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Already watched by smart-scholarship</t>
+          <t>Already watched by optiver-ready-trader</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>SMART Scholarship</t>
+          <t>Optiver Ready Trader Go</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -14964,29 +15010,25 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>https://www.smartscholarship.org/smart</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t>Verified 2026-09-26: scholarship-for-service - requires civilian employment with the Department of War after graduation. 'open annually from August 1 to the first Friday in December'.</t>
-        </is>
-      </c>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Already watched by stevens-high-frequency-trading</t>
+          <t>Already watched by physics-surp</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Stevens High Frequency Trading Competition 2026</t>
+          <t>Stanford Physics / Applied Physics / SLAC Summer Research Program</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -14996,248 +15038,244 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
+          <t>https://physics.stanford.edu/undergraduate/undergraduate-research</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
+          <t>Verified 2026-10-08: 'We accept applications from current freshmen, sophomores, and juniors.' Gate: Fellowships go to 'Stanford undergraduate Physics and Engineering Physics majors, plus undeclared first-year students who are considering Physics/Engineering Physics as a major'. 'For beginning students, research experience is not required.' Base stipend $8,500 plus need-based supplement up to $1,500, ten weeks. Applicant finds a faculty mentor; 2026 Part 1 was due noon Jan 16, Part 2 Feb 20.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Already watched by surim-apply</t>
+          <t>Already watched by princeton-stock-pitch</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Stanford SURIM</t>
+          <t>Princeton Stock Pitch (Tiger Investments)</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>VIA CLUB</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>https://mathematics.stanford.edu/</t>
+          <t>https://princetonstockpitch.vercel.app/</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>8 weeks, $8,500 + up to $1,500 need-based. Needs MATH 56/61CM/61DM/110/113/115 first, and 2 letters (1 from Stanford Math). | Checked 2026-09-26: SURIM has its own page at surim.stanford.edu/apply-surim, which is watched; the listed mathematics.stanford.edu is kept.</t>
+          <t>Verified 2026-10-08 on the official page: "open to student investment clubs nationwide"; "Who can enter: Open to all student investment clubs. Teams of 3-5 members." Free, virtual; 3-5 page memo, presentation and model on one long or short idea over $2B market cap. Tentative 2027 dates: submissions Mar 5, finalists Mar 12, live Zoom finals Mar 15. Prize pool ~$6,000. Entry is through a club, so a Stanford investing club team is the route in; no class-year restriction stated.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>Already watched by symsys-summer</t>
+          <t>Already watched by purdue-srop</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Stanford SymSys Summer Internships</t>
+          <t>Purdue Summer Research Opportunities Program (SROP)</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>https://symsys.stanford.edu/opportunities/research/summer-undergraduate-research-symbolic-systems</t>
+          <t>https://www.purdue.edu/academics/ogsps/ogrs/summer-research-opportunity-program/</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>$8,500 + up to $1,500. A real backdoor if funds remain after the priority window. | Corrected 2026-10-08: website was the department homepage https://symsys.stanford.edu/; the programme page is /opportunities/research/summer-undergraduate-research-symbolic-systems (the older /opportunitiesresearch/summer-internship-program path redirects there), now watched by symsys-summer. It says: 'Only Stanford University undergraduates may apply. Priority is given to students who have declared a major in Symbolic Systems.' 2026 priority period ran Feb 18 - Mar 9; after Mar 9 internships 'may be offered to any current undergraduate who meets VPUE eligibility criteria, if funds are still available.'</t>
+          <t>Part of the Big Ten Academic Alliance SROP. Page states eligibility includes US citizens, permanent residents, refugees and asylees enrolled at a US institution; read the full criteria on the page.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Already watched by texas-usit-competitions</t>
+          <t>Already watched by pwp-careers</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Texas Stock Pitch (UT Austin USIT)</t>
+          <t>Perella Weinberg careers</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Finance program</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>https://www.texasusit.org/competitions-overviews</t>
+          <t>https://pwpartners.com/careers/</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08 on USIT's competitions overview: Texas Stock Pitch is "the largest stock pitch competition in the Southern United States" and "provides undergraduate students from all over the nation with the opportunity to demonstrate their proficiency in investment research, valuation, and presentation"; up to $5,000 in prizes; "This competition will be held in February 2027." Class-year rules, team size and fees are not on this page and were not verified: texasstockpitch.com does not resolve (DNS) and stockpitch.texasusit.org, linked from the page, returned 404 on 2026-10-08. The same page lists Texas Charity Pitch (Nov 2026) and the Analyst Group Stock Pitch, which is for USIT's own members only.</t>
+          <t>Simplify's list names the U.S. Perella Weinberg Advisory Prep Program for sophomores. No ATS link found on the page.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Already watched by treehacks</t>
+          <t>Already watched by ramp-ashby</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>TreeHacks</t>
+          <t>Ramp Emerging Talent</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>https://treehacks.com/</t>
+          <t>https://ramp.com/emerging-talent</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'open to any enrolled college student'; Stanford students get priority by the priority deadline.</t>
+          <t>Verified 2026-09-30: 'For interns: anyone who will be registered in an accredited 4 year university post-internship.' Fintech SWE internships posted on Ashby 'ramp'.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Already watched by twosigma-campus</t>
+          <t>Already watched by raymondjames-workday</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma New Seekers Summit</t>
+          <t>Raymond James early careers board</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Finance program</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/new-seekers-summit/</t>
+          <t>https://raymondjames.wd1.myworkdayjobs.com/raymondjamesearlycareers</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'gives first-and second-year undergraduates the opportunity to delve into the world of Data Scientists and Quantitative Researchers.' QR seminars, networking, interview prep. www.twosigma.com is WP Engine, which 403s the Actions runner, so it is not watched as page_text; the posting should appear on twosigma-campus (Avature).</t>
+          <t>Raymond James's early-careers Workday board. 2026-10-11 carried '2026 Fall Virtual Sophomore Program: Investment Banking Bootcamp for 2028 Summer Analyst Opportunities'. The sophomore-opportunities page on raymondjames.com returns 403, so the board is the route.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>Already watched by uchicago-bluechips-pitch</t>
+          <t>Already watched by reufinder-freshmen</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>UChicago Blue Chips Intercollegiate Stock Pitch Competition</t>
+          <t>REU Finder - freshman-eligible filter</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>https://www.tbc.uchicago.edu/pitch-competition</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>Verified 2026-10-08 on the official page: "Our 2026 Intercollegiate Stock Pitch Competition has concluded. Please stay tuned for our 2027 Intercollegiate Stock Pitch Competition, which will be held in March 2027." Requirements: "Teams of 1-3 undergraduates (cross-school teams and international students welcome)", long-only pitch on an NYSE/Nasdaq company over $2B, 15-slide deck plus valuation model, blind submission. 2026 prizes $1,200 / $800 / $400; virtual finals. No class-year restriction stated.</t>
-        </is>
-      </c>
+          <t>https://reufinder.com/programs-for-freshmen/</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>Already watched by uchicago-trading-competition</t>
+          <t>Already watched by sandia-students</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>UChicago Trading Competition</t>
+          <t>Sandia National Laboratories student internships</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>https://tradingcompetition.uchicago.edu/</t>
+          <t>https://www.sandia.gov/careers/careers/students-and-postdocs/</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>PRIORITY TO TEAMS WITHOUT PRIOR TRADING WORK EXPERIENCE - structurally favors freshmen. April event, $15k+ prizes.</t>
+          <t>Undergraduate and graduate internships across Sandia's sites.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>Already watched by umich-uic</t>
+          <t>Already watched by scudem</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>ENGAGE Undergraduate Investment Conference Stock Pitch (Michigan UIC)</t>
+          <t>SCUDEM XI 2026</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -15245,68 +15283,68 @@
           <t>Competition</t>
         </is>
       </c>
-      <c r="D104" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>https://www.umichuic.com/</t>
+          <t>https://www.contest.comap.com/scudem/index.html</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08 on the official site. Home page: the conference "will return to the University of Michigan on Saturday, November 14th 2026. Stock Pitch submissions are now live." UIC 19 page: "Each team of 2-4 members will pitch an equity, long or short"; "Each team must submit a one-pager here highlighting their idea by October 28th, 2026 at 11:59pm"; "These one-pagers will be evaluated on a rolling basis". Invited teams must each buy a conference ticket. FAQ: "groups can even be comprised of people across different organizations or different universities." Prizes $7,500 / $2,000 / $1,000. Hosted by Michigan Interactive Investments at Ross. Undergraduate conference; no class-year restriction stated.</t>
+          <t>Verified 2026-09-30: COMAP's differential-equations modelling challenge. FAQ: 'open to teams of 3 undergraduate or high school students. Each team must have a coach (typically a faculty member or instructor).' Ends in a 10-minute video judged by at least 3 judges. Needs a faculty coach.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>Already watched by underclassmen-cruz</t>
+          <t>Already watched by seo-tech</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>underclassmen-opportunities (Cruz-Lopez)</t>
+          <t>SEO Tech Developer + First-Year Academy</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>USE WEEKLY</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
+          <t>https://tech.seo-usa.org/</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>Better maintained than zapplyjobs, with open/closing-soon flags. Heavy on ambassador programs - filter hard.</t>
+          <t>Verified 2026-09-26: 'Enrolled as a sophomore'; the Academy is for 'first-year college students'. Page says 'All are welcome to apply'; SEO is a diversity organisation, so confirm eligibility by hand.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>Already watched by weiss-greenhouse</t>
+          <t>Already watched by sfhacks</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Weiss Asset Management 2027 Underclassmen Fellowship</t>
+          <t>SF Hacks</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -15316,29 +15354,29 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/weissassetmanagement</t>
+          <t>https://www.sfhacks.io/</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08 on Weiss's Greenhouse board (posting 8831639002, updated 2026-10-02): "This program is only open to current Freshmen and Sophomores (Classes of 2029 and 2030)". Two-day in-person programme in Boston "on January 7th and 8th, 2027"; "All selected students will have their transportation and hotel costs fully covered"; "High-performing fellows may be considered for future internship opportunities." No identity gate stated. No application deadline stated in the posting, so apply early. weissasset.com/careers carries no programme text (893 chars), so the board is the watch target. Source: research notes, Freshman finance programs 2026-27.</t>
+          <t>Verified 2026-10-08: 'All students are welcome, from high school through university.' 'We are not offering travel reimbursements this year.' San Francisco.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Already watched by witg-stock-pitch</t>
+          <t>Already watched by sfi-ucr</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>WITG x Fundamental Edge Stock Pitch Competition (Penn)</t>
+          <t>SFI Undergraduate Complexity Research</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -15348,29 +15386,29 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>https://www.pennwitg.com/competition</t>
+          <t>https://www.santafe.edu/engage/learn/programs/undergraduate-complexity-research</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08 on the official page: "The competition is open to all university undergraduate students across the United States and internationally who wish to participate. Teams are allowed to cross-register with undergraduates from any school and are able to register in groups of 2-4." Fourth annual edition, hosted by the Wharton Investment &amp; Trading Group. Dates: registration opened Sep 21, 2026; "Registration and First Round Executive Summary Deadline ... Monday, October 19, 2026 at 11:59PM EST"; finalists Oct 22; final round Oct 28 at Huntsman Hall with a virtual option. No class-year restriction stated.</t>
+          <t>Verified 2026-09-26: 'for current undergraduate students. Prior research experience is not required'; 'return to this page in November 2026'.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>Already watched by worldquant-iqc</t>
+          <t>Already watched by siepr-ugrf-academic-year</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>WorldQuant IQC / BRAIN</t>
+          <t>SIEPR Undergraduate Research Fellows (academic year)</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -15380,312 +15418,312 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>https://www.worldquant.com/brain/iqc/</t>
+          <t>https://siepr.stanford.edu/programs/undergraduate-student-opportunities/undergraduate-research-fellows-program/academic-year</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>Teams of 1-4 from one university. $100k pool. Solo entry allowed. Huge field (140k+ registrations) so mid-table means little.</t>
+          <t>Verified 2026-10-08: 'UGRFs must be enrolled as full-time undergraduate students at Stanford.' SOLO's listing 'SIEPR Undergraduate Research Program AY 2026-2027' says Deadline: Rolling deadline, Open To: Freshman, Sophomore, Junior. Part-time RA on posted economic-policy faculty projects, paid via payroll 'for up to 15 hours a week'. Online application with current course list, resume and cover letter. 'Applications for 2026 Autumn quarter are now open'; the Autumn programme runs September 22 to December 4, 2026.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Already watched by yhack</t>
+          <t>Already watched by siepr-ugrf-summer</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>YHack</t>
+          <t>SIEPR Summer Undergraduate Research Fellows</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>https://www.yhack.org/</t>
+          <t>https://siepr.stanford.edu/programs/undergraduate-student-opportunities/undergraduate-research-fellows-program/siepr-summer</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'Accepted participants will have the opportunity to apply for travel reimbursement. We expect to be able to support many participants traveling from the East Coast, with additional consideration given' beyond it. Yale.</t>
+          <t>Verified 2026-09-30: 'Participants must be current Stanford undergraduates during the summer quarter.' 10 weeks, $8,500, economic-policy research RA with SIEPR faculty. | Checked 2026-10-08: page unchanged in substance; now watched by siepr-ugrf-summer.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>Already watched by yutc</t>
+          <t>Already watched by simplify-2027</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Yale Undergraduate Trading Competition</t>
+          <t>SimplifyJobs Summer 2027 Internships</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>https://www.yale.edu/</t>
+          <t>https://github.com/SimplifyJobs/Summer2027-Internships</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>$10,000+ in prizes, nationwide. | Checked 2026-09-26: the competition's own site is yutc.org (a JavaScript page, watched with render_js); the listed yale.edu is kept.</t>
+          <t>613 roles, 94 quant, but no class-year tagging and almost all target penultimate-year students.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by sjhacks</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Bank of America APAC Quant Conference</t>
+          <t>SJHacks</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D111" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>https://www.bofa.com/</t>
+          <t>https://www.sjhacks.com/</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Verified 2026-10-08: 'SJHacks is a 24-hour in-person hackathon at San Jose State University'; 2026 edition April 25-26 at Guildhouse, San Jose. The page states no eligibility rule and nothing about travel.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by smart-scholarship</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Bridgewater Rising Fellows</t>
+          <t>SMART Scholarship</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D112" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>https://www.bridgewater.com/risingfellowsprogram</t>
+          <t>https://www.smartscholarship.org/smart</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>CORRECTED: first-year eligible BUT targets backgrounds underrepresented in the industry, recruiting via HBCUs, O4U, BLK Capital, Prep for Prep. | Checked 2026-09-26: now redirects to the generic /working-at-bridgewater page. Kept: it may reopen.</t>
+          <t>Verified 2026-09-26: scholarship-for-service - requires civilian employment with the Department of War after graduation. 'open annually from August 1 to the first Friday in December'.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by stevens-high-frequency-trading</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>CQA Young Professionals Event</t>
+          <t>Stevens High Frequency Trading Competition 2026</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D113" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
+          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by surim-apply</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Citadel Securities Ignite</t>
+          <t>Stanford SURIM</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D114" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
+          <t>https://mathematics.stanford.edu/</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>Invite-only weeklong program for sophomore women.</t>
+          <t>8 weeks, $8,500 + up to $1,500 need-based. Needs MATH 56/61CM/61DM/110/113/115 first, and 2 letters (1 from Stanford Math). | Checked 2026-09-26: SURIM has its own page at surim.stanford.edu/apply-surim, which is watched; the listed mathematics.stanford.edu is kept.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by symsys-summer</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Coding it Forward - Civic Digital Fellowship</t>
+          <t>Stanford SymSys Summer Internships</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D115" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>https://www.codingitforward.com/fellowship</t>
+          <t>https://symsys.stanford.edu/opportunities/research/summer-undergraduate-research-symbolic-systems</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>TRAP - appears on most underclassmen lists but 2026 required graduating May 2025-Dec 2027. Diary for junior year.</t>
+          <t>$8,500 + up to $1,500. A real backdoor if funds remain after the priority window. | Corrected 2026-10-08: website was the department homepage https://symsys.stanford.edu/; the programme page is /opportunities/research/summer-undergraduate-research-symbolic-systems (the older /opportunitiesresearch/summer-internship-program path redirects there), now watched by symsys-summer. It says: 'Only Stanford University undergraduates may apply. Priority is given to students who have declared a major in Symbolic Systems.' 2026 priority period ran Feb 18 - Mar 9; after Mar 9 internships 'may be offered to any current undergraduate who meets VPUE eligibility criteria, if funds are still available.'</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by texas-usit-competitions</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Discovery Fellowship</t>
+          <t>Texas Stock Pitch (UT Austin USIT)</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D116" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://www.texasusit.org/competitions-overviews</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>Verified 2026-10-08 on USIT's competitions overview: Texas Stock Pitch is "the largest stock pitch competition in the Southern United States" and "provides undergraduate students from all over the nation with the opportunity to demonstrate their proficiency in investment research, valuation, and presentation"; up to $5,000 in prizes; "This competition will be held in February 2027." Class-year rules, team size and fees are not on this page and were not verified: texasstockpitch.com does not resolve (DNS) and stockpitch.texasusit.org, linked from the page, returned 404 on 2026-10-08. The same page lists Texas Charity Pitch (Nov 2026) and the Analyst Group Stock Pitch, which is for USIT's own members only.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by treehacks</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Latitude Fellowship</t>
+          <t>TreeHacks</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D117" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://treehacks.com/</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>Verified 2026-09-26: 'open to any enrolled college student'; Stanford students get priority by the priority deadline.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by twosigma-campus</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw London Insight Programme</t>
+          <t>Two Sigma New Seekers Summit</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -15693,95 +15731,95 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D118" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/additional-experiences</t>
+          <t>https://www.twosigma.com/new-seekers-summit/</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. | Checked 2026-09-26: campus.deshaw.com/additional-experiences now redirects to the campus root (which lists London Insight as closed). Kept.</t>
+          <t>Verified 2026-09-30: 'gives first-and second-year undergraduates the opportunity to delve into the world of Data Scientists and Quantitative Researchers.' QR seminars, networking, interview prep. www.twosigma.com is WP Engine, which 403s the Actions runner, so it is not watched as page_text; the posting should appear on twosigma-campus (Avature).</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by uchicago-bluechips-pitch</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Momentum Fellowship</t>
+          <t>UChicago Blue Chips Intercollegiate Stock Pitch Competition</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D119" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://www.tbc.uchicago.edu/pitch-competition</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>Verified 2026-10-08 on the official page: "Our 2026 Intercollegiate Stock Pitch Competition has concluded. Please stay tuned for our 2027 Intercollegiate Stock Pitch Competition, which will be held in March 2027." Requirements: "Teams of 1-3 undergraduates (cross-school teams and international students welcome)", long-only pitch on an NYSE/Nasdaq company over $2B, 15-slide deck plus valuation model, blind submission. 2026 prizes $1,200 / $800 / $400; virtual finals. No class-year restriction stated.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by uchicago-trading-competition</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Databento partner quant events (Shanghai, London)</t>
+          <t>UChicago Trading Competition</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D120" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>https://databento.com/</t>
+          <t>https://tradingcompetition.uchicago.edu/</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>PRIORITY TO TEAMS WITHOUT PRIOR TRADING WORK EXPERIENCE - structurally favors freshmen. April event, $15k+ prizes.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by umich-uic</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
+          <t>ENGAGE Undergraduate Investment Conference Stock Pitch (Michigan UIC)</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -15789,63 +15827,63 @@
           <t>Competition</t>
         </is>
       </c>
-      <c r="D121" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>https://en.tmtpost.com/post/7752441</t>
+          <t>https://www.umichuic.com/</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Verified 2026-10-08 on the official site. Home page: the conference "will return to the University of Michigan on Saturday, November 14th 2026. Stock Pitch submissions are now live." UIC 19 page: "Each team of 2-4 members will pitch an equity, long or short"; "Each team must submit a one-pager here highlighting their idea by October 28th, 2026 at 11:59pm"; "These one-pagers will be evaluated on a rolling basis". Invited teams must each buy a conference ticket. FAQ: "groups can even be comprised of people across different organizations or different universities." Prizes $7,500 / $2,000 / $1,000. Hosted by Michigan Interactive Investments at Ross. Undergraduate conference; no class-year restriction stated.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by underclassmen-cruz</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>IMC EU Business Course</t>
+          <t>underclassmen-opportunities (Cruz-Lopez)</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D122" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
+          <t>https://github.com/Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Better maintained than zapplyjobs, with open/closing-soon flags. Heavy on ambassador programs - filter hard.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by weiss-greenhouse</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>IMC UK Masterclass</t>
+          <t>Weiss Asset Management 2027 Underclassmen Fellowship</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -15853,59 +15891,63 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D123" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>https://careers.imc.com/</t>
+          <t>https://job-boards.greenhouse.io/weissassetmanagement</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>Geographic exclusion - excludes US-based students.</t>
+          <t>Verified 2026-10-08 on Weiss's Greenhouse board (posting 8831639002, updated 2026-10-02): "This program is only open to current Freshmen and Sophomores (Classes of 2029 and 2030)". Two-day in-person programme in Boston "on January 7th and 8th, 2027"; "All selected students will have their transportation and hotel costs fully covered"; "High-performing fellows may be considered for future internship opportunities." No identity gate stated. No application deadline stated in the posting, so apply early. weissasset.com/careers carries no programme text (893 chars), so the board is the watch target. Source: research notes, Freshman finance programs 2026-27.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by witg-stock-pitch</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>IMC WiT (Women in Technology)</t>
+          <t>WITG x Fundamental Edge Stock Pitch Competition (Penn)</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D124" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>https://careers.imc.com/us/en/student-opportunities</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr"/>
+          <t>https://www.pennwitg.com/competition</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-10-08 on the official page: "The competition is open to all university undergraduate students across the United States and internationally who wish to participate. Teams are allowed to cross-register with undergraduates from any school and are able to register in groups of 2-4." Fourth annual edition, hosted by the Wharton Investment &amp; Trading Group. Dates: registration opened Sep 21, 2026; "Registration and First Round Executive Summary Deadline ... Monday, October 19, 2026 at 11:59PM EST"; finalists Oct 22; final round Oct 28 at Huntsman Hall with a virtual option. No class-year restriction stated.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by worldquant-iqc</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>IMC Women in Trading and Engineering</t>
+          <t>WorldQuant IQC / BRAIN</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -15913,83 +15955,83 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D125" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
+          <t>https://www.worldquant.com/brain/iqc/</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Teams of 1-4 from one university. $100k pool. Solo entry allowed. Huge field (140k+ registrations) so mid-table means little.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by yhack</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan Data for Good Hackathon</t>
+          <t>YHack</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D126" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>https://careers.jpmorgan.com/</t>
+          <t>https://www.yhack.org/</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>That is a junior-year window; a first-year does not qualify.</t>
+          <t>Verified 2026-10-08: 'Accepted participants will have the opportunity to apply for travel reimbursement. We expect to be able to support many participants traveling from the East Coast, with additional consideration given' beyond it. Yale.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by yutc</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Jane Street FOCUS and IN FOCUS</t>
+          <t>Yale Undergraduate Trading Competition</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D127" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://www.yale.edu/</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>Barriers-to-access criteria (first-gen, Pell-eligible, under-resourced school). Read criteria yourself.</t>
+          <t>$10,000+ in prizes, nationwide. | Checked 2026-09-26: the competition's own site is yutc.org (a JavaScript page, watched with render_js); the listed yale.edu is kept.</t>
         </is>
       </c>
     </row>
@@ -16001,12 +16043,12 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Graduate Research Fellowship</t>
+          <t>Bank of America APAC Quant Conference</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
@@ -16016,10 +16058,14 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F128" s="3" t="inlineStr"/>
+          <t>https://www.bofa.com/</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -16029,7 +16075,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Jane Street INSIGHT</t>
+          <t>Bridgewater Rising Fellows</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -16044,12 +16090,12 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
+          <t>https://www.bridgewater.com/risingfellowsprogram</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>For women, transgender and gender-expansive people.</t>
+          <t>CORRECTED: first-year eligible BUT targets backgrounds underrepresented in the industry, recruiting via HBCUs, O4U, BLK Capital, Prep for Prep. | Checked 2026-09-26: now redirects to the generic /working-at-bridgewater page. Kept: it may reopen.</t>
         </is>
       </c>
     </row>
@@ -16061,12 +16107,12 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Jane Street JSIP</t>
+          <t>CQA Young Professionals Event</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
@@ -16076,12 +16122,12 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/jsip/</t>
+          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>Multi-week paid NYC program, $12,500 scholarship - but requires having experienced barriers to access in CS. | Checked 2026-09-26: now redirects to the programs-and-events index, which does not list JSIP. Kept: it may reopen for the next cycle.</t>
+          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -16093,7 +16139,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Visiting Researcher / Prefaculty</t>
+          <t>Citadel Securities Ignite</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -16108,10 +16154,14 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F131" s="3" t="inlineStr"/>
+          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>Invite-only weeklong program for sophomore women.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -16121,12 +16171,12 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Jane Street WiSE</t>
+          <t>Coding it Forward - Civic Digital Fellowship</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
@@ -16136,12 +16186,12 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://www.codingitforward.com/fellowship</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>Women / trans / gender-expansive students.</t>
+          <t>TRAP - appears on most underclassmen lists but 2026 required graduating May 2025-Dec 2027. Diary for junior year.</t>
         </is>
       </c>
     </row>
@@ -16153,12 +16203,12 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>KNHack 2026 Research Challenge (Mexico)</t>
+          <t>D. E. Shaw Discovery Fellowship</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
@@ -16168,12 +16218,12 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>https://kaxanuk.mx/kn-hack</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
@@ -16185,12 +16235,12 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>MIT Pokerbots</t>
+          <t>D. E. Shaw Latitude Fellowship</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
@@ -16200,12 +16250,12 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>https://pokerbots.org/</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>Must be able to register for MIT IAP classes; a team member needs MIT certificates for the competition server.</t>
+          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
@@ -16217,12 +16267,12 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Meta University</t>
+          <t>D. E. Shaw London Insight Programme</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
@@ -16230,14 +16280,14 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>https://campus.deshaw.com/additional-experiences</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>Discontinued with no replacement. Ignore any list that still includes it.</t>
+          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. | Checked 2026-09-26: campus.deshaw.com/additional-experiences now redirects to the campus root (which lists London Insight as closed). Kept.</t>
         </is>
       </c>
     </row>
@@ -16249,7 +16299,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Optiver Career Kickstarter: Women in Tech</t>
+          <t>D. E. Shaw Momentum Fellowship</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -16264,12 +16314,12 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
@@ -16281,12 +16331,12 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Optiver Quantitative Intern Summer 2027</t>
+          <t>Databento partner quant events (Shanghai, London)</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D137" s="8" t="inlineStr">
@@ -16296,12 +16346,12 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+          <t>https://databento.com/</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>Highest pay in the industry, but a first-year is too early.</t>
+          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -16313,12 +16363,12 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Optiver regional recruitment events (non-US)</t>
+          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
@@ -16328,12 +16378,12 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/recruitment-events/</t>
+          <t>https://en.tmtpost.com/post/7752441</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -16345,7 +16395,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>PEAK6 Trading Bootcamp</t>
+          <t>IMC EU Business Course</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -16360,12 +16410,12 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>https://peak6.com/campus/</t>
+          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>One week, $25-31.25/hr, two sessions (May and Aug).</t>
+          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -16377,12 +16427,12 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Palantir Path</t>
+          <t>IMC UK Masterclass</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
@@ -16390,12 +16440,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F140" s="3" t="inlineStr"/>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.imc.com/</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>Geographic exclusion - excludes US-based students.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -16405,7 +16459,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>Point72 Academy</t>
+          <t>IMC WiT (Women in Technology)</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -16420,14 +16474,10 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>https://point72.com/point72-academy/</t>
-        </is>
-      </c>
-      <c r="F141" s="3" t="inlineStr">
-        <is>
-          <t>NOT an underclassman program. 10-month paid post-grad program, $125k base. 2027 class wants Dec 2026-Jul 2027 grads.</t>
-        </is>
-      </c>
+          <t>https://careers.imc.com/us/en/student-opportunities</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -16437,7 +16487,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Days for Women (all tracks)</t>
+          <t>IMC Women in Trading and Engineering</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -16452,10 +16502,14 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="F142" s="3" t="inlineStr"/>
+          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -16465,12 +16519,12 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma College Mentor Connect</t>
+          <t>JPMorgan Data for Good Hackathon</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr">
@@ -16480,12 +16534,12 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
+          <t>https://careers.jpmorgan.com/</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>6-week remote mentorship on open-source projects.</t>
+          <t>That is a junior-year window; a first-year does not qualify.</t>
         </is>
       </c>
     </row>
@@ -16497,7 +16551,7 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Diversity Undergraduate Scholarship</t>
+          <t>Jane Street FOCUS and IN FOCUS</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -16512,10 +16566,14 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
-        </is>
-      </c>
-      <c r="F144" s="3" t="inlineStr"/>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>Barriers-to-access criteria (first-gen, Pell-eligible, under-resourced school). Read criteria yourself.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -16525,7 +16583,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma PhD Fellowship</t>
+          <t>Jane Street Graduate Research Fellowship</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -16540,7 +16598,7 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/graduate-students/phd-fellowships/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr"/>
@@ -16553,7 +16611,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Virtu Financial Women's Winternship</t>
+          <t>Jane Street INSIGHT</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -16568,10 +16626,14 @@
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>https://www.virtu.com/careers/</t>
-        </is>
-      </c>
-      <c r="F146" s="3" t="inlineStr"/>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>For women, transgender and gender-expansive people.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
@@ -16581,12 +16643,12 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Wharton Global High School Investment Competition</t>
+          <t>Jane Street JSIP</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D147" s="8" t="inlineStr">
@@ -16596,12 +16658,12 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/jsip/</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Multi-week paid NYC program, $12,500 scholarship - but requires having experienced barriers to access in CS. | Checked 2026-09-26: now redirects to the programs-and-events index, which does not list JSIP. Kept: it may reopen for the next cycle.</t>
         </is>
       </c>
     </row>
@@ -16613,12 +16675,12 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Women in Quantitative Finance Americas Conference</t>
+          <t>Jane Street Visiting Researcher / Prefaculty</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
@@ -16628,14 +16690,10 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>https://www.wbstraining.com/events/wqfa</t>
-        </is>
-      </c>
-      <c r="F148" s="3" t="inlineStr">
-        <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -16645,12 +16703,12 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Women in Quantitative Finance London Conference</t>
+          <t>Jane Street WiSE</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D149" s="8" t="inlineStr">
@@ -16660,49 +16718,573 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Women / trans / gender-expansive students.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>KNHack 2026 Research Challenge (Mexico)</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D150" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>https://kaxanuk.mx/kn-hack</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>MIT Pokerbots</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D151" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>https://pokerbots.org/</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>Must be able to register for MIT IAP classes; a team member needs MIT certificates for the competition server.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>Meta University</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D152" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>Discontinued with no replacement. Ignore any list that still includes it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>Optiver Career Kickstarter: Women in Tech</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D153" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>Optiver Quantitative Intern Summer 2027</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D154" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>Highest pay in the industry, but a first-year is too early.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>Optiver regional recruitment events (non-US)</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D155" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>https://optiver.com/recruitment-events/</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>PEAK6 Trading Bootcamp</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D156" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>https://peak6.com/campus/</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>One week, $25-31.25/hr, two sessions (May and Aug).</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>Palantir Path</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D157" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>Point72 Academy</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D158" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>https://point72.com/point72-academy/</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>NOT an underclassman program. 10-month paid post-grad program, $125k base. 2027 class wants Dec 2026-Jul 2027 grads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>SIG Sophomore Discovery Days for Women (all tracks)</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D159" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma College Mentor Connect</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D160" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>6-week remote mentorship on open-source projects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma Diversity Undergraduate Scholarship</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D161" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma PhD Fellowship</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D162" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twosigma.com/graduate-students/phd-fellowships/</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>Virtu Financial Women's Winternship</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D163" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.virtu.com/careers/</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>Wharton Global High School Investment Competition</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D164" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>Women in Quantitative Finance Americas Conference</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D165" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wbstraining.com/events/wqfa</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>Women in Quantitative Finance London Conference</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D166" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
           <t>You cannot apply (STALE)</t>
         </is>
       </c>
-      <c r="B150" s="3" t="inlineStr">
+      <c r="B167" s="3" t="inlineStr">
         <is>
           <t>zapplyjobs underclassmen-internships</t>
         </is>
       </c>
-      <c r="C150" s="3" t="inlineStr">
+      <c r="C167" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D150" s="8" t="inlineStr">
+      <c r="D167" s="8" t="inlineStr">
         <is>
           <t>STALE</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
+      <c r="E167" s="4" t="inlineStr">
         <is>
           <t>https://github.com/zapplyjobs/underclassmen-internships</t>
         </is>
       </c>
-      <c r="F150" s="3" t="inlineStr">
+      <c r="F167" s="3" t="inlineStr">
         <is>
           <t>Right shape, but entries and links are out of date.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F150"/>
+  <autoFilter ref="A1:F167"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -16837,20 +17419,37 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId164"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -15114,7 +15114,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Already watched by pwp-careers</t>
+          <t>Already watched by pwp-events</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -15139,7 +15139,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>Simplify's list names the U.S. Perella Weinberg Advisory Prep Program for sophomores. No ATS link found on the page.</t>
+          <t>Simplify's list names the U.S. Perella Weinberg Advisory Prep Program for sophomores. No ATS link found on the page. Correction 2026-10-20: the intern page links a tal.net board (pwpcareers.tal.net); its events feed lists the U.S. Advisory Prep Program.</t>
         </is>
       </c>
     </row>
